--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922CD3AB-BFAA-E94D-B7CD-64F4EE293C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2DB0FE-4745-4B31-B752-49F884610EAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="504" windowWidth="28800" windowHeight="17496" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -28,10 +28,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1242,19 +1242,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:K310"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>45</v>
       </c>
@@ -1268,7 +1268,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1278,7 +1278,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1292,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1348,7 +1348,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,7 +1374,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1481,7 +1481,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1495,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1577,7 +1577,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1730,7 +1730,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,7 +1744,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1758,7 +1758,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1772,7 +1772,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1800,7 +1800,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1814,7 +1814,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1826,7 +1826,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1979,7 +1979,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -2007,7 +2007,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -2021,7 +2021,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -2063,7 +2063,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2228,7 +2228,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2242,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2270,7 +2270,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2312,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2324,7 +2324,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2454,7 +2454,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2468,7 +2468,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2482,7 +2482,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2510,7 +2510,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2524,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2550,7 +2550,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2704,7 +2704,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2718,7 +2718,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2732,7 +2732,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2746,7 +2746,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2930,7 +2930,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2958,7 +2958,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2986,7 +2986,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -3000,7 +3000,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -3014,7 +3014,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3026,7 +3026,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3254,7 +3254,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3268,7 +3268,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3282,7 +3282,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3296,7 +3296,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3338,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3350,7 +3350,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>90</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3576,7 +3576,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3604,7 +3604,7 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
@@ -3618,7 +3618,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3632,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3660,7 +3660,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>97</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>100</v>
       </c>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>101</v>
       </c>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>102</v>
       </c>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>104</v>
       </c>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>105</v>
       </c>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>106</v>
       </c>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>107</v>
       </c>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>108</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>109</v>
       </c>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>110</v>
       </c>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>111</v>
       </c>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>112</v>
       </c>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>113</v>
       </c>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>114</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>116</v>
       </c>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>117</v>
       </c>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>118</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4152,7 +4152,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4167,7 +4167,7 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
@@ -4182,7 +4182,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
@@ -4197,7 +4197,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4212,7 +4212,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4242,7 +4242,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4255,7 +4255,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4305,7 +4305,7 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>124</v>
       </c>
@@ -4329,7 +4329,7 @@
       <c r="I170" s="8"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>127</v>
       </c>
@@ -4353,7 +4353,7 @@
       <c r="I171" s="8"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>129</v>
       </c>
@@ -4377,7 +4377,7 @@
       <c r="I172" s="8"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>131</v>
       </c>
@@ -4401,7 +4401,7 @@
       <c r="I173" s="8"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>122</v>
       </c>
@@ -4427,7 +4427,7 @@
       <c r="I174" s="8"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>132</v>
       </c>
@@ -4453,7 +4453,7 @@
       <c r="I175" s="8"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>134</v>
       </c>
@@ -4479,7 +4479,7 @@
       <c r="I176" s="8"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>136</v>
       </c>
@@ -4505,7 +4505,7 @@
       <c r="I177" s="8"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>138</v>
       </c>
@@ -4531,7 +4531,7 @@
       <c r="I178" s="8"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>139</v>
       </c>
@@ -4557,7 +4557,7 @@
       <c r="I179" s="8"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="8" t="s">
         <v>140</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="I180" s="8"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="8" t="s">
         <v>143</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="I181" s="8"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="8" t="s">
         <v>146</v>
       </c>
@@ -4635,7 +4635,7 @@
       <c r="I182" s="8"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="8" t="s">
         <v>148</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="I183" s="8"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="8" t="s">
         <v>150</v>
       </c>
@@ -4687,7 +4687,7 @@
       <c r="I184" s="8"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="8" t="s">
         <v>152</v>
       </c>
@@ -4713,7 +4713,7 @@
       <c r="I185" s="8"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
         <v>154</v>
       </c>
@@ -4739,7 +4739,7 @@
       <c r="I186" s="8"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4750,7 +4750,7 @@
       <c r="H187" s="2"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4765,7 +4765,7 @@
       <c r="H188" s="8"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
@@ -4780,7 +4780,7 @@
       <c r="H189" s="8"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4808,7 +4808,7 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="8" t="s">
         <v>121</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="8" t="s">
         <v>122</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>55</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>29</v>
       </c>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4979,7 +4979,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
@@ -5007,7 +5007,7 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -5035,7 +5035,7 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -5063,7 +5063,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -5075,7 +5075,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="8" t="s">
         <v>158</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="8" t="s">
         <v>122</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5206,7 +5206,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5220,7 +5220,7 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
@@ -5234,7 +5234,7 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
@@ -5248,7 +5248,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5262,7 +5262,7 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
@@ -5290,7 +5290,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5302,7 +5302,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="8" t="s">
         <v>161</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>85</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="8" t="s">
         <v>158</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="8" t="s">
         <v>163</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="8" t="s">
         <v>159</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5480,7 +5480,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5494,7 +5494,7 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
@@ -5508,7 +5508,7 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5536,7 +5536,7 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
@@ -5564,7 +5564,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5576,7 +5576,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="8" t="s">
         <v>159</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>85</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="8" t="s">
         <v>158</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="8" t="s">
         <v>161</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>29</v>
       </c>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5753,7 +5753,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5781,7 +5781,7 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5809,7 +5809,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5823,7 +5823,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5849,7 +5849,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>168</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5978,7 +5978,7 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
@@ -5992,7 +5992,7 @@
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
@@ -6006,7 +6006,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
@@ -6020,7 +6020,7 @@
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -6034,7 +6034,7 @@
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
@@ -6048,7 +6048,7 @@
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="19" t="s">
         <v>201</v>
       </c>
@@ -6074,7 +6074,7 @@
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
@@ -6086,7 +6086,7 @@
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="17" t="s">
         <v>185</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>47</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="17" t="s">
         <v>202</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="17" t="s">
         <v>204</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="17" t="s">
         <v>206</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>101</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>100</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="18" t="s">
         <v>207</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>37</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="18" t="s">
         <v>195</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="18" t="s">
         <v>105</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="18" t="s">
         <v>208</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="18" t="s">
         <v>209</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="18" t="s">
         <v>210</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="18" t="s">
         <v>115</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="18" t="s">
         <v>211</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="18" t="s">
         <v>212</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="18" t="s">
         <v>196</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="18" t="s">
         <v>108</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="18" t="s">
         <v>213</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="18" t="s">
         <v>214</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="18" t="s">
         <v>215</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="18" t="s">
         <v>216</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="18" t="s">
         <v>217</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="3"/>
@@ -6654,7 +6654,7 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="19" t="s">
         <v>0</v>
       </c>
@@ -6668,7 +6668,7 @@
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="19" t="s">
         <v>2</v>
       </c>
@@ -6682,7 +6682,7 @@
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="19" t="s">
         <v>3</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -6710,7 +6710,7 @@
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="19" t="s">
         <v>5</v>
       </c>
@@ -6724,7 +6724,7 @@
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="19" t="s">
         <v>8</v>
       </c>
@@ -6738,7 +6738,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="19" t="s">
         <v>10</v>
       </c>
@@ -6750,7 +6750,7 @@
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="5" t="s">
         <v>11</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="17" t="s">
         <v>206</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>55</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>225</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>227</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>229</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>231</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>233</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>88</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>235</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>90</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>95</v>
       </c>
@@ -7040,17 +7040,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7064,7 +7064,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -7078,7 +7078,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -7092,7 +7092,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -7120,7 +7120,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -7146,7 +7146,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>180</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>239</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>240</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>242</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -7516,7 +7516,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -7530,7 +7530,7 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
@@ -7544,7 +7544,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -7558,7 +7558,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
@@ -7586,7 +7586,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -7600,7 +7600,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -7612,7 +7612,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>165</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>185</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>180</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>239</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>240</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>242</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
@@ -7982,7 +7982,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -7996,7 +7996,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>2</v>
       </c>
@@ -8010,7 +8010,7 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>3</v>
       </c>
@@ -8024,7 +8024,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>5</v>
       </c>
@@ -8038,7 +8038,7 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>6</v>
       </c>
@@ -8052,7 +8052,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>8</v>
       </c>
@@ -8066,7 +8066,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
@@ -8078,7 +8078,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>11</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>171</v>
       </c>
@@ -8128,7 +8128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>40</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>78</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>35</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>154</v>
       </c>
@@ -8368,40 +8368,40 @@
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B69" s="15"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B74" s="15"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="13"/>
       <c r="C80" s="8"/>
@@ -8419,17 +8419,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8443,7 +8443,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8457,7 +8457,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8471,7 +8471,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8485,7 +8485,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8499,7 +8499,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8513,7 +8513,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8525,7 +8525,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>188</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>189</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>191</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>192</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>194</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>195</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>196</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>198</v>
       </c>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>199</v>
       </c>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9187,7 +9187,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9201,7 +9201,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
@@ -9215,7 +9215,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9229,7 +9229,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9243,7 +9243,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9257,7 +9257,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9271,7 +9271,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9283,7 +9283,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>175</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
         <v>185</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>176</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>178</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>180</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>181</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>188</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>189</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>190</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>192</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>194</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>195</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>196</v>
       </c>
@@ -9872,7 +9872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>198</v>
       </c>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>199</v>
       </c>
@@ -9944,18 +9944,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -10003,12 +10003,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>224</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>221</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>223</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2DB0FE-4745-4B31-B752-49F884610EAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9142D67-A209-BB41-8050-817D763891D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="28800" windowHeight="17496" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -28,10 +28,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1242,19 +1242,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:K310"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>45</v>
       </c>
@@ -1268,7 +1268,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1278,7 +1278,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1292,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1348,7 +1348,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,7 +1374,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1481,7 +1481,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1495,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1577,7 +1577,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1730,7 +1730,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,7 +1744,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1758,7 +1758,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1772,7 +1772,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1800,7 +1800,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1814,7 +1814,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1826,7 +1826,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1979,7 +1979,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -2007,7 +2007,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -2021,7 +2021,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -2063,7 +2063,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2228,7 +2228,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2242,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2270,7 +2270,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2312,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2324,7 +2324,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2454,7 +2454,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2468,7 +2468,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2482,7 +2482,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2510,7 +2510,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2524,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2550,7 +2550,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2704,7 +2704,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2718,7 +2718,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2732,7 +2732,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2746,7 +2746,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2930,7 +2930,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2958,7 +2958,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2986,7 +2986,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -3000,7 +3000,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -3014,7 +3014,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3026,7 +3026,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3254,7 +3254,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3268,7 +3268,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3282,7 +3282,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3296,7 +3296,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3338,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3350,7 +3350,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>90</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3576,7 +3576,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3604,7 +3604,7 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
@@ -3618,7 +3618,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3632,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3660,7 +3660,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>97</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>100</v>
       </c>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>101</v>
       </c>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>102</v>
       </c>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>104</v>
       </c>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>105</v>
       </c>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>106</v>
       </c>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>107</v>
       </c>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>108</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>109</v>
       </c>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>110</v>
       </c>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>111</v>
       </c>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>112</v>
       </c>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>113</v>
       </c>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>114</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>116</v>
       </c>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>117</v>
       </c>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>118</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4152,7 +4152,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4167,7 +4167,7 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
@@ -4182,7 +4182,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
@@ -4197,7 +4197,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4212,7 +4212,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4242,7 +4242,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4255,7 +4255,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4305,7 +4305,7 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>124</v>
       </c>
@@ -4329,7 +4329,7 @@
       <c r="I170" s="8"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>127</v>
       </c>
@@ -4353,7 +4353,7 @@
       <c r="I171" s="8"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>129</v>
       </c>
@@ -4377,7 +4377,7 @@
       <c r="I172" s="8"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>131</v>
       </c>
@@ -4401,7 +4401,7 @@
       <c r="I173" s="8"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>122</v>
       </c>
@@ -4427,7 +4427,7 @@
       <c r="I174" s="8"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>132</v>
       </c>
@@ -4453,7 +4453,7 @@
       <c r="I175" s="8"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>134</v>
       </c>
@@ -4479,7 +4479,7 @@
       <c r="I176" s="8"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>136</v>
       </c>
@@ -4505,7 +4505,7 @@
       <c r="I177" s="8"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>138</v>
       </c>
@@ -4531,7 +4531,7 @@
       <c r="I178" s="8"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>139</v>
       </c>
@@ -4557,7 +4557,7 @@
       <c r="I179" s="8"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="8" t="s">
         <v>140</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="I180" s="8"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
         <v>143</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="I181" s="8"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
         <v>146</v>
       </c>
@@ -4635,7 +4635,7 @@
       <c r="I182" s="8"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
         <v>148</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="I183" s="8"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
         <v>150</v>
       </c>
@@ -4687,7 +4687,7 @@
       <c r="I184" s="8"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
         <v>152</v>
       </c>
@@ -4713,7 +4713,7 @@
       <c r="I185" s="8"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
         <v>154</v>
       </c>
@@ -4739,7 +4739,7 @@
       <c r="I186" s="8"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4750,7 +4750,7 @@
       <c r="H187" s="2"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4765,7 +4765,7 @@
       <c r="H188" s="8"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
@@ -4780,7 +4780,7 @@
       <c r="H189" s="8"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4808,7 +4808,7 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
         <v>121</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="8" t="s">
         <v>122</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>55</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>29</v>
       </c>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4979,7 +4979,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
@@ -5007,7 +5007,7 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -5035,7 +5035,7 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -5063,7 +5063,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -5075,7 +5075,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
         <v>158</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
         <v>122</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5206,7 +5206,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5220,7 +5220,7 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
@@ -5234,7 +5234,7 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
@@ -5248,7 +5248,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5262,7 +5262,7 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
@@ -5290,7 +5290,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5302,7 +5302,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="8" t="s">
         <v>161</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>85</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="8" t="s">
         <v>158</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="8" t="s">
         <v>163</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="8" t="s">
         <v>159</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5480,7 +5480,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5494,7 +5494,7 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
@@ -5508,7 +5508,7 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5536,7 +5536,7 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
@@ -5564,7 +5564,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5576,7 +5576,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="8" t="s">
         <v>159</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>85</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="8" t="s">
         <v>158</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="8" t="s">
         <v>161</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>29</v>
       </c>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5753,7 +5753,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5781,7 +5781,7 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5809,7 +5809,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5823,7 +5823,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5849,7 +5849,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="5" t="s">
         <v>168</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5978,7 +5978,7 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
@@ -5992,7 +5992,7 @@
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
@@ -6006,7 +6006,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
@@ -6020,7 +6020,7 @@
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -6034,7 +6034,7 @@
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
@@ -6048,7 +6048,7 @@
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="19" t="s">
         <v>201</v>
       </c>
@@ -6074,7 +6074,7 @@
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
@@ -6086,7 +6086,7 @@
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="17" t="s">
         <v>185</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>47</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="17" t="s">
         <v>202</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="17" t="s">
         <v>204</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="17" t="s">
         <v>206</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>101</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>100</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="18" t="s">
         <v>207</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>37</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="18" t="s">
         <v>195</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="18" t="s">
         <v>105</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="18" t="s">
         <v>208</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="18" t="s">
         <v>209</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="18" t="s">
         <v>210</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="18" t="s">
         <v>115</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="18" t="s">
         <v>211</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="18" t="s">
         <v>212</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="18" t="s">
         <v>196</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="18" t="s">
         <v>108</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="18" t="s">
         <v>213</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="18" t="s">
         <v>214</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="18" t="s">
         <v>215</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="18" t="s">
         <v>216</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="18" t="s">
         <v>217</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="3"/>
@@ -6654,7 +6654,7 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="19" t="s">
         <v>0</v>
       </c>
@@ -6668,7 +6668,7 @@
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="19" t="s">
         <v>2</v>
       </c>
@@ -6682,7 +6682,7 @@
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="19" t="s">
         <v>3</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -6710,7 +6710,7 @@
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="19" t="s">
         <v>5</v>
       </c>
@@ -6724,7 +6724,7 @@
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="19" t="s">
         <v>8</v>
       </c>
@@ -6738,7 +6738,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="19" t="s">
         <v>10</v>
       </c>
@@ -6750,7 +6750,7 @@
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
         <v>11</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="17" t="s">
         <v>206</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>55</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>225</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>227</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>229</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>231</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>233</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>88</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>235</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>90</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>95</v>
       </c>
@@ -7040,17 +7040,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7064,7 +7064,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -7078,7 +7078,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -7092,7 +7092,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -7120,7 +7120,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -7146,7 +7146,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>180</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>239</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>240</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>242</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -7516,7 +7516,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -7530,7 +7530,7 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
@@ -7544,7 +7544,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -7558,7 +7558,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
@@ -7586,7 +7586,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -7600,7 +7600,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -7612,7 +7612,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>165</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>185</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>180</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>239</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>240</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
         <v>242</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
@@ -7982,7 +7982,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -7996,7 +7996,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>2</v>
       </c>
@@ -8010,7 +8010,7 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>3</v>
       </c>
@@ -8024,7 +8024,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>5</v>
       </c>
@@ -8038,7 +8038,7 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>6</v>
       </c>
@@ -8052,7 +8052,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>8</v>
       </c>
@@ -8066,7 +8066,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
@@ -8078,7 +8078,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>11</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>171</v>
       </c>
@@ -8128,7 +8128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>40</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>78</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>35</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>154</v>
       </c>
@@ -8368,40 +8368,40 @@
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B69" s="15"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B74" s="15"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="8"/>
       <c r="B80" s="13"/>
       <c r="C80" s="8"/>
@@ -8419,17 +8419,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8443,7 +8443,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8457,7 +8457,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8471,7 +8471,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8485,7 +8485,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8499,7 +8499,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8513,7 +8513,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8525,7 +8525,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>188</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>189</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>191</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>192</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>194</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>195</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>196</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>198</v>
       </c>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>199</v>
       </c>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9187,7 +9187,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9201,7 +9201,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
@@ -9215,7 +9215,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9229,7 +9229,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9243,7 +9243,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9257,7 +9257,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9271,7 +9271,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9283,7 +9283,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>175</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="17" t="s">
         <v>185</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>176</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>178</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>180</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>181</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>188</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>189</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>190</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>192</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>194</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>195</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>196</v>
       </c>
@@ -9872,7 +9872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>198</v>
       </c>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>199</v>
       </c>
@@ -9944,18 +9944,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -10003,12 +10003,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>224</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>221</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>223</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>94</v>
       </c>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9142D67-A209-BB41-8050-817D763891D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9185937C-A6BC-4128-BB0F-ACC0A8102AE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="504" windowWidth="28800" windowHeight="17496" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -22,17 +22,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -863,7 +852,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -926,6 +915,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1242,19 +1232,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:K310"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>45</v>
       </c>
@@ -1268,7 +1258,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1278,7 +1268,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1282,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1306,7 +1296,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1320,7 +1310,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1334,7 +1324,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1348,7 +1338,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1352,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,7 +1364,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1400,7 +1390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1424,7 +1414,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1448,7 +1438,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1471,7 +1461,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1481,7 +1471,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1485,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1509,7 +1499,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1513,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1537,7 +1527,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1551,7 +1541,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1565,7 +1555,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1577,7 +1567,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1603,7 +1593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1627,7 +1617,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1651,7 +1641,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1674,7 +1664,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1697,7 +1687,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1720,7 +1710,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1730,7 +1720,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,7 +1734,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1758,7 +1748,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1772,7 +1762,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1786,7 +1776,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1800,7 +1790,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1814,7 +1804,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1826,7 +1816,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1852,7 +1842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1876,7 +1866,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1900,7 +1890,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1923,7 +1913,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1946,7 +1936,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1969,7 +1959,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1979,7 +1969,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1993,7 +1983,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -2007,7 +1997,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -2021,7 +2011,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2025,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2039,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -2063,7 +2053,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2075,7 +2065,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2101,7 +2091,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2125,7 +2115,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2149,7 +2139,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2172,7 +2162,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2195,7 +2185,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2218,7 +2208,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2228,7 +2218,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2232,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2256,7 +2246,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2270,7 +2260,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2284,7 +2274,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2288,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2302,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2324,7 +2314,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2350,7 +2340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2374,7 +2364,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2398,7 +2388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -2421,7 +2411,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -2444,7 +2434,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2454,7 +2444,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2468,7 +2458,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2482,7 +2472,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2496,7 +2486,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2510,7 +2500,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2514,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2538,7 +2528,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2550,7 +2540,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2600,7 +2590,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2624,7 +2614,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2648,7 +2638,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2671,7 +2661,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -2694,7 +2684,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2704,7 +2694,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2718,7 +2708,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2732,7 +2722,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2746,7 +2736,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2760,7 +2750,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2774,7 +2764,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2788,7 +2778,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2800,7 +2790,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2826,7 +2816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -2850,7 +2840,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -2874,7 +2864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -2897,7 +2887,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -2920,7 +2910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2930,7 +2920,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2944,7 +2934,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2958,7 +2948,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -2972,7 +2962,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2986,7 +2976,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -3000,7 +2990,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -3014,7 +3004,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3026,7 +3016,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -3052,7 +3042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -3076,7 +3066,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -3100,7 +3090,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -3124,7 +3114,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -3148,7 +3138,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -3172,7 +3162,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3196,7 +3186,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -3220,7 +3210,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -3244,7 +3234,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3254,7 +3244,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3268,7 +3258,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3282,7 +3272,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3296,7 +3286,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3310,7 +3300,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3324,7 +3314,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3328,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3350,7 +3340,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3376,7 +3366,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -3400,7 +3390,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -3425,7 +3415,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -3450,7 +3440,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>90</v>
       </c>
@@ -3475,7 +3465,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -3500,7 +3490,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -3521,7 +3511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -3542,7 +3532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -3566,7 +3556,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3576,7 +3566,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3590,7 +3580,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3604,7 +3594,7 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
@@ -3618,7 +3608,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3622,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3646,7 +3636,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3660,7 +3650,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3672,7 +3662,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3698,7 +3688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>97</v>
       </c>
@@ -3722,7 +3712,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>100</v>
       </c>
@@ -3743,7 +3733,7 @@
       </c>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -3764,7 +3754,7 @@
       </c>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>101</v>
       </c>
@@ -3785,7 +3775,7 @@
       </c>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>102</v>
       </c>
@@ -3806,7 +3796,7 @@
       </c>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -3827,7 +3817,7 @@
       </c>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>104</v>
       </c>
@@ -3848,7 +3838,7 @@
       </c>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>105</v>
       </c>
@@ -3869,7 +3859,7 @@
       </c>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>106</v>
       </c>
@@ -3890,7 +3880,7 @@
       </c>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>107</v>
       </c>
@@ -3911,7 +3901,7 @@
       </c>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>108</v>
       </c>
@@ -3932,7 +3922,7 @@
       </c>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>109</v>
       </c>
@@ -3953,7 +3943,7 @@
       </c>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>110</v>
       </c>
@@ -3974,7 +3964,7 @@
       </c>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>111</v>
       </c>
@@ -3995,7 +3985,7 @@
       </c>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>112</v>
       </c>
@@ -4016,7 +4006,7 @@
       </c>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>113</v>
       </c>
@@ -4037,7 +4027,7 @@
       </c>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>114</v>
       </c>
@@ -4058,7 +4048,7 @@
       </c>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -4079,7 +4069,7 @@
       </c>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>116</v>
       </c>
@@ -4100,7 +4090,7 @@
       </c>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>117</v>
       </c>
@@ -4121,7 +4111,7 @@
       </c>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>118</v>
       </c>
@@ -4142,7 +4132,7 @@
       </c>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4152,7 +4142,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4167,7 +4157,7 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
@@ -4182,7 +4172,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
@@ -4197,7 +4187,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4212,7 +4202,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4227,7 +4217,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4242,7 +4232,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4255,7 +4245,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4282,7 +4272,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4305,7 +4295,7 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>124</v>
       </c>
@@ -4329,7 +4319,7 @@
       <c r="I170" s="8"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>127</v>
       </c>
@@ -4353,7 +4343,7 @@
       <c r="I171" s="8"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>129</v>
       </c>
@@ -4377,7 +4367,7 @@
       <c r="I172" s="8"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>131</v>
       </c>
@@ -4401,7 +4391,7 @@
       <c r="I173" s="8"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>122</v>
       </c>
@@ -4427,7 +4417,7 @@
       <c r="I174" s="8"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>132</v>
       </c>
@@ -4453,7 +4443,7 @@
       <c r="I175" s="8"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>134</v>
       </c>
@@ -4479,7 +4469,7 @@
       <c r="I176" s="8"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>136</v>
       </c>
@@ -4505,7 +4495,7 @@
       <c r="I177" s="8"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>138</v>
       </c>
@@ -4531,7 +4521,7 @@
       <c r="I178" s="8"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>139</v>
       </c>
@@ -4557,7 +4547,7 @@
       <c r="I179" s="8"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="8" t="s">
         <v>140</v>
       </c>
@@ -4583,7 +4573,7 @@
       <c r="I180" s="8"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="8" t="s">
         <v>143</v>
       </c>
@@ -4609,7 +4599,7 @@
       <c r="I181" s="8"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="8" t="s">
         <v>146</v>
       </c>
@@ -4635,7 +4625,7 @@
       <c r="I182" s="8"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="8" t="s">
         <v>148</v>
       </c>
@@ -4661,7 +4651,7 @@
       <c r="I183" s="8"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="8" t="s">
         <v>150</v>
       </c>
@@ -4687,7 +4677,7 @@
       <c r="I184" s="8"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="8" t="s">
         <v>152</v>
       </c>
@@ -4713,7 +4703,7 @@
       <c r="I185" s="8"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
         <v>154</v>
       </c>
@@ -4739,7 +4729,7 @@
       <c r="I186" s="8"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4750,7 +4740,7 @@
       <c r="H187" s="2"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4765,7 +4755,7 @@
       <c r="H188" s="8"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
@@ -4780,7 +4770,7 @@
       <c r="H189" s="8"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
@@ -4794,7 +4784,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4808,7 +4798,7 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
@@ -4822,7 +4812,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4836,7 +4826,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4848,7 +4838,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4874,7 +4864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="8" t="s">
         <v>121</v>
       </c>
@@ -4898,7 +4888,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="8" t="s">
         <v>122</v>
       </c>
@@ -4922,7 +4912,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>55</v>
       </c>
@@ -4946,7 +4936,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>29</v>
       </c>
@@ -4969,7 +4959,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4979,7 +4969,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4993,7 +4983,7 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
@@ -5007,7 +4997,7 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
@@ -5021,7 +5011,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -5035,7 +5025,7 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
@@ -5049,7 +5039,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -5063,7 +5053,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -5075,7 +5065,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5101,7 +5091,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="8" t="s">
         <v>158</v>
       </c>
@@ -5125,7 +5115,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="8" t="s">
         <v>122</v>
       </c>
@@ -5149,7 +5139,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -5173,7 +5163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -5196,7 +5186,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5206,7 +5196,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5220,7 +5210,7 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
@@ -5234,7 +5224,7 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
@@ -5248,7 +5238,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5262,7 +5252,7 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
@@ -5276,7 +5266,7 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
@@ -5290,7 +5280,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5302,7 +5292,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5328,7 +5318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="8" t="s">
         <v>161</v>
       </c>
@@ -5352,7 +5342,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>85</v>
       </c>
@@ -5376,7 +5366,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="8" t="s">
         <v>158</v>
       </c>
@@ -5400,7 +5390,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="8" t="s">
         <v>163</v>
       </c>
@@ -5424,7 +5414,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="8" t="s">
         <v>159</v>
       </c>
@@ -5448,7 +5438,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -5470,7 +5460,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5480,7 +5470,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5494,7 +5484,7 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
@@ -5508,7 +5498,7 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
@@ -5522,7 +5512,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5536,7 +5526,7 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
@@ -5550,7 +5540,7 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
@@ -5564,7 +5554,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5576,7 +5566,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5602,7 +5592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="8" t="s">
         <v>159</v>
       </c>
@@ -5626,7 +5616,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>85</v>
       </c>
@@ -5650,7 +5640,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="8" t="s">
         <v>158</v>
       </c>
@@ -5674,7 +5664,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5697,7 +5687,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="8" t="s">
         <v>161</v>
       </c>
@@ -5721,7 +5711,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>29</v>
       </c>
@@ -5743,7 +5733,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5753,7 +5743,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5767,7 +5757,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5781,7 +5771,7 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
@@ -5795,7 +5785,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5809,7 +5799,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5823,7 +5813,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5837,7 +5827,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5849,7 +5839,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5875,7 +5865,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5899,7 +5889,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>168</v>
       </c>
@@ -5923,7 +5913,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5945,7 +5935,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5968,7 +5958,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5978,7 +5968,7 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
@@ -5992,7 +5982,7 @@
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
@@ -6006,7 +5996,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
@@ -6020,7 +6010,7 @@
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -6034,7 +6024,7 @@
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
@@ -6048,7 +6038,7 @@
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
@@ -6062,7 +6052,7 @@
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="19" t="s">
         <v>201</v>
       </c>
@@ -6074,7 +6064,7 @@
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
@@ -6086,7 +6076,7 @@
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
@@ -6112,7 +6102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="17" t="s">
         <v>185</v>
       </c>
@@ -6136,7 +6126,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>47</v>
       </c>
@@ -6160,7 +6150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="17" t="s">
         <v>202</v>
       </c>
@@ -6184,7 +6174,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="17" t="s">
         <v>204</v>
       </c>
@@ -6208,7 +6198,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="17" t="s">
         <v>206</v>
       </c>
@@ -6232,7 +6222,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -6253,7 +6243,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>101</v>
       </c>
@@ -6274,7 +6264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>100</v>
       </c>
@@ -6295,7 +6285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="18" t="s">
         <v>207</v>
       </c>
@@ -6316,7 +6306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>37</v>
       </c>
@@ -6337,7 +6327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="18" t="s">
         <v>195</v>
       </c>
@@ -6358,7 +6348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="18" t="s">
         <v>105</v>
       </c>
@@ -6379,7 +6369,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="18" t="s">
         <v>208</v>
       </c>
@@ -6400,7 +6390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="18" t="s">
         <v>209</v>
       </c>
@@ -6421,7 +6411,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="18" t="s">
         <v>210</v>
       </c>
@@ -6442,7 +6432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="18" t="s">
         <v>115</v>
       </c>
@@ -6463,7 +6453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="18" t="s">
         <v>211</v>
       </c>
@@ -6484,7 +6474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="18" t="s">
         <v>212</v>
       </c>
@@ -6504,7 +6494,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="18" t="s">
         <v>196</v>
       </c>
@@ -6524,7 +6514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="18" t="s">
         <v>108</v>
       </c>
@@ -6544,7 +6534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="18" t="s">
         <v>213</v>
       </c>
@@ -6564,7 +6554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="18" t="s">
         <v>214</v>
       </c>
@@ -6584,7 +6574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="18" t="s">
         <v>215</v>
       </c>
@@ -6604,7 +6594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="18" t="s">
         <v>216</v>
       </c>
@@ -6624,7 +6614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="18" t="s">
         <v>217</v>
       </c>
@@ -6644,7 +6634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="3"/>
@@ -6654,7 +6644,7 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="19" t="s">
         <v>0</v>
       </c>
@@ -6668,7 +6658,7 @@
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="19" t="s">
         <v>2</v>
       </c>
@@ -6682,7 +6672,7 @@
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="19" t="s">
         <v>3</v>
       </c>
@@ -6696,7 +6686,7 @@
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -6710,7 +6700,7 @@
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="19" t="s">
         <v>5</v>
       </c>
@@ -6724,7 +6714,7 @@
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="19" t="s">
         <v>8</v>
       </c>
@@ -6738,7 +6728,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="19" t="s">
         <v>10</v>
       </c>
@@ -6750,7 +6740,7 @@
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="5" t="s">
         <v>11</v>
       </c>
@@ -6776,7 +6766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="17" t="s">
         <v>206</v>
       </c>
@@ -6800,7 +6790,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>55</v>
       </c>
@@ -6824,7 +6814,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>225</v>
       </c>
@@ -6847,7 +6837,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>227</v>
       </c>
@@ -6870,7 +6860,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>229</v>
       </c>
@@ -6893,7 +6883,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>231</v>
       </c>
@@ -6916,7 +6906,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>233</v>
       </c>
@@ -6939,7 +6929,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>88</v>
       </c>
@@ -6962,7 +6952,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>235</v>
       </c>
@@ -6985,7 +6975,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>90</v>
       </c>
@@ -7008,7 +6998,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>95</v>
       </c>
@@ -7040,17 +7030,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7064,7 +7054,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -7078,7 +7068,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -7092,7 +7082,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -7106,7 +7096,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -7120,7 +7110,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -7134,7 +7124,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -7146,7 +7136,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -7172,7 +7162,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -7196,7 +7186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7220,7 +7210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -7244,7 +7234,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7267,7 +7257,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>180</v>
       </c>
@@ -7291,7 +7281,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>239</v>
       </c>
@@ -7314,7 +7304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>240</v>
       </c>
@@ -7338,7 +7328,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -7361,7 +7351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>242</v>
       </c>
@@ -7384,7 +7374,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7404,7 +7394,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7424,7 +7414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -7445,7 +7435,7 @@
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7466,7 +7456,7 @@
       </c>
       <c r="H21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7486,7 +7476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7506,7 +7496,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -7516,7 +7506,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -7530,7 +7520,7 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
@@ -7544,7 +7534,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -7558,7 +7548,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
@@ -7572,7 +7562,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
@@ -7586,7 +7576,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -7600,7 +7590,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -7612,7 +7602,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
@@ -7638,7 +7628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>165</v>
       </c>
@@ -7662,7 +7652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -7686,7 +7676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>185</v>
       </c>
@@ -7710,7 +7700,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -7733,7 +7723,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>180</v>
       </c>
@@ -7757,7 +7747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>239</v>
       </c>
@@ -7780,7 +7770,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>240</v>
       </c>
@@ -7804,7 +7794,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -7827,7 +7817,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>242</v>
       </c>
@@ -7850,7 +7840,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -7870,7 +7860,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -7890,7 +7880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -7911,7 +7901,7 @@
       </c>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -7932,7 +7922,7 @@
       </c>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -7952,7 +7942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -7972,7 +7962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
@@ -7982,7 +7972,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -7996,7 +7986,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>2</v>
       </c>
@@ -8010,7 +8000,7 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>3</v>
       </c>
@@ -8024,7 +8014,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>5</v>
       </c>
@@ -8038,7 +8028,7 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>6</v>
       </c>
@@ -8052,7 +8042,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>8</v>
       </c>
@@ -8066,7 +8056,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
@@ -8078,7 +8068,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>11</v>
       </c>
@@ -8104,7 +8094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>171</v>
       </c>
@@ -8128,7 +8118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>40</v>
       </c>
@@ -8152,7 +8142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>78</v>
       </c>
@@ -8176,7 +8166,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -8200,7 +8190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -8220,7 +8210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -8243,7 +8233,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -8263,7 +8253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>35</v>
       </c>
@@ -8283,7 +8273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -8303,7 +8293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -8324,7 +8314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -8345,7 +8335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>154</v>
       </c>
@@ -8368,40 +8358,41 @@
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="28"/>
       <c r="B69" s="15"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B74" s="15"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="13"/>
       <c r="C80" s="8"/>
@@ -8419,17 +8410,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8443,7 +8434,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8457,7 +8448,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8471,7 +8462,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8485,7 +8476,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8499,7 +8490,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8513,7 +8504,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8525,7 +8516,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8551,7 +8542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -8575,7 +8566,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8599,7 +8590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -8623,7 +8614,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -8646,7 +8637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -8670,7 +8661,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -8694,7 +8685,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -8718,7 +8709,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -8742,7 +8733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -8766,7 +8757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -8791,7 +8782,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -8814,7 +8805,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -8834,7 +8825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8854,7 +8845,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>188</v>
       </c>
@@ -8874,7 +8865,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -8894,7 +8885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -8914,7 +8905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>189</v>
       </c>
@@ -8934,7 +8925,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -8954,7 +8945,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>191</v>
       </c>
@@ -8974,7 +8965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>192</v>
       </c>
@@ -8994,7 +8985,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -9014,7 +9005,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -9034,7 +9025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -9054,7 +9045,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>194</v>
       </c>
@@ -9074,7 +9065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>195</v>
       </c>
@@ -9094,7 +9085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>196</v>
       </c>
@@ -9114,7 +9105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -9134,7 +9125,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>198</v>
       </c>
@@ -9155,7 +9146,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>199</v>
       </c>
@@ -9177,7 +9168,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9187,7 +9178,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9201,7 +9192,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
@@ -9215,7 +9206,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9229,7 +9220,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9243,7 +9234,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9257,7 +9248,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9271,7 +9262,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9283,7 +9274,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9309,7 +9300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>175</v>
       </c>
@@ -9333,7 +9324,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9357,7 +9348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
         <v>185</v>
       </c>
@@ -9381,7 +9372,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -9404,7 +9395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>176</v>
       </c>
@@ -9428,7 +9419,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>178</v>
       </c>
@@ -9452,7 +9443,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -9476,7 +9467,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>180</v>
       </c>
@@ -9500,7 +9491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -9524,7 +9515,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>181</v>
       </c>
@@ -9549,7 +9540,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -9572,7 +9563,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -9592,7 +9583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9612,7 +9603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>188</v>
       </c>
@@ -9632,7 +9623,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9652,7 +9643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9672,7 +9663,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>189</v>
       </c>
@@ -9692,7 +9683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>190</v>
       </c>
@@ -9712,7 +9703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -9732,7 +9723,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>192</v>
       </c>
@@ -9752,7 +9743,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -9772,7 +9763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -9792,7 +9783,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -9812,7 +9803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>194</v>
       </c>
@@ -9832,7 +9823,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>195</v>
       </c>
@@ -9852,7 +9843,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>196</v>
       </c>
@@ -9872,7 +9863,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -9892,7 +9883,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>198</v>
       </c>
@@ -9913,7 +9904,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>199</v>
       </c>
@@ -9944,18 +9935,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9963,7 +9954,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9971,7 +9962,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9979,7 +9970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -9987,7 +9978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9995,7 +9986,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -10003,12 +9994,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10034,7 +10025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>224</v>
       </c>
@@ -10057,7 +10048,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -10080,7 +10071,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -10104,7 +10095,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10126,7 +10117,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>221</v>
       </c>
@@ -10149,7 +10140,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -10172,7 +10163,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10192,7 +10183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -10212,7 +10203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>223</v>
       </c>
@@ -10235,7 +10226,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A917FF2B-A6EC-4384-9790-E3D110C37661}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF93657-23D2-B240-B91E-134D555924B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="510" windowWidth="28800" windowHeight="17490" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -23,6 +23,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -904,7 +915,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -955,7 +966,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1284,19 +1294,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:H159"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>45</v>
       </c>
@@ -1310,7 +1320,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1320,7 +1330,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1344,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1348,7 +1358,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1362,7 +1372,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1376,7 +1386,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1390,7 +1400,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1414,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1416,7 +1426,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1442,7 +1452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1466,7 +1476,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1490,7 +1500,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1513,7 +1523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1523,7 +1533,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1547,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1551,7 +1561,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1565,7 +1575,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1579,7 +1589,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1593,7 +1603,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1607,7 +1617,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1619,7 +1629,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1645,7 +1655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1669,7 +1679,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1693,7 +1703,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1716,7 +1726,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1739,7 +1749,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1762,7 +1772,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1772,7 +1782,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1786,7 +1796,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1800,7 +1810,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1814,7 +1824,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1828,7 +1838,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1842,7 +1852,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1856,7 +1866,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1868,7 +1878,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1894,7 +1904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -1918,7 +1928,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -1942,7 +1952,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -1965,7 +1975,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -1988,7 +1998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2011,7 +2021,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -2021,7 +2031,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -2035,7 +2045,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -2049,7 +2059,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -2063,7 +2073,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2077,7 +2087,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -2091,7 +2101,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -2105,7 +2115,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2117,7 +2127,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2143,7 +2153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -2167,7 +2177,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2191,7 +2201,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -2214,7 +2224,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2237,7 +2247,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2260,7 +2270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2270,7 +2280,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2284,7 +2294,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2298,7 +2308,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2312,7 +2322,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2326,7 +2336,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2340,7 +2350,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2354,7 +2364,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2366,7 +2376,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2392,7 +2402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -2416,7 +2426,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -2440,7 +2450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -2463,7 +2473,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>54</v>
       </c>
@@ -2486,7 +2496,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2496,7 +2506,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2510,7 +2520,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2524,7 +2534,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2538,7 +2548,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2552,7 +2562,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2566,7 +2576,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2580,7 +2590,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2592,7 +2602,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2618,7 +2628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -2642,7 +2652,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>64</v>
       </c>
@@ -2666,7 +2676,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2690,7 +2700,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -2713,7 +2723,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -2736,7 +2746,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2746,7 +2756,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2760,7 +2770,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2774,7 +2784,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2788,7 +2798,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2802,7 +2812,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2816,7 +2826,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2830,7 +2840,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2842,7 +2852,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2868,7 +2878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>81</v>
       </c>
@@ -2892,7 +2902,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>76</v>
       </c>
@@ -2916,7 +2926,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -2939,7 +2949,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>54</v>
       </c>
@@ -2962,7 +2972,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2972,7 +2982,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2986,7 +2996,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -3000,7 +3010,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -3014,7 +3024,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -3028,7 +3038,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -3042,7 +3052,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -3056,7 +3066,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3068,7 +3078,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -3094,7 +3104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -3118,7 +3128,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>50</v>
       </c>
@@ -3142,7 +3152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -3166,7 +3176,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>62</v>
       </c>
@@ -3190,7 +3200,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>70</v>
       </c>
@@ -3214,7 +3224,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>74</v>
       </c>
@@ -3238,7 +3248,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>77</v>
       </c>
@@ -3262,7 +3272,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>81</v>
       </c>
@@ -3286,7 +3296,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3296,7 +3306,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3310,7 +3320,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3324,7 +3334,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3338,7 +3348,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3352,7 +3362,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3366,7 +3376,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3380,7 +3390,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3392,7 +3402,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3418,7 +3428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="17" t="s">
         <v>133</v>
       </c>
@@ -3442,7 +3452,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>253</v>
       </c>
@@ -3459,14 +3469,14 @@
         <v>21</v>
       </c>
       <c r="F123" s="8"/>
-      <c r="G123" s="24" t="s">
+      <c r="G123" t="s">
         <v>20</v>
       </c>
       <c r="H123" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="17" t="s">
         <v>149</v>
       </c>
@@ -3483,14 +3493,14 @@
         <v>24</v>
       </c>
       <c r="F124" s="8"/>
-      <c r="G124" s="24" t="s">
+      <c r="G124" t="s">
         <v>20</v>
       </c>
       <c r="H124" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="17" t="s">
         <v>151</v>
       </c>
@@ -3507,14 +3517,14 @@
         <v>8</v>
       </c>
       <c r="F125" s="8"/>
-      <c r="G125" s="24" t="s">
+      <c r="G125" t="s">
         <v>20</v>
       </c>
       <c r="H125" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="17" t="s">
         <v>192</v>
       </c>
@@ -3531,21 +3541,21 @@
         <v>9</v>
       </c>
       <c r="F126" s="8"/>
-      <c r="G126" s="24" t="s">
+      <c r="G126" t="s">
         <v>20</v>
       </c>
       <c r="H126" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>29</v>
       </c>
       <c r="B127" s="9">
         <v>5.8947368421052686E-3</v>
       </c>
-      <c r="C127" s="24" t="s">
+      <c r="C127" t="s">
         <v>30</v>
       </c>
       <c r="E127" t="s">
@@ -3554,18 +3564,18 @@
       <c r="F127" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G127" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G127" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>92</v>
       </c>
       <c r="B128" s="15">
         <v>2.2105263157894801E-6</v>
       </c>
-      <c r="C128" s="24" t="s">
+      <c r="C128" t="s">
         <v>30</v>
       </c>
       <c r="E128" t="s">
@@ -3574,18 +3584,18 @@
       <c r="F128" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G128" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>91</v>
       </c>
       <c r="B129" s="15">
         <v>2.10526315789474E-6</v>
       </c>
-      <c r="C129" s="24" t="s">
+      <c r="C129" t="s">
         <v>30</v>
       </c>
       <c r="E129" t="s">
@@ -3594,18 +3604,18 @@
       <c r="F129" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G129" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G129" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="18" t="s">
         <v>153</v>
       </c>
       <c r="B130" s="15">
         <v>1.05263157894737E-7</v>
       </c>
-      <c r="C130" s="24" t="s">
+      <c r="C130" t="s">
         <v>30</v>
       </c>
       <c r="E130" t="s">
@@ -3614,18 +3624,18 @@
       <c r="F130" t="s">
         <v>135</v>
       </c>
-      <c r="G130" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G130" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>37</v>
       </c>
       <c r="B131" s="15">
         <v>1.8842105263157901E-5</v>
       </c>
-      <c r="C131" s="24" t="s">
+      <c r="C131" t="s">
         <v>30</v>
       </c>
       <c r="E131" t="s">
@@ -3634,18 +3644,18 @@
       <c r="F131" t="s">
         <v>135</v>
       </c>
-      <c r="G131" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G131" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="18" t="s">
         <v>143</v>
       </c>
       <c r="B132" s="15">
         <v>5.7894736842105305E-7</v>
       </c>
-      <c r="C132" s="24" t="s">
+      <c r="C132" t="s">
         <v>30</v>
       </c>
       <c r="E132" t="s">
@@ -3654,18 +3664,18 @@
       <c r="F132" t="s">
         <v>135</v>
       </c>
-      <c r="G132" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G132" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="18" t="s">
         <v>93</v>
       </c>
       <c r="B133" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C133" s="24" t="s">
+      <c r="C133" t="s">
         <v>30</v>
       </c>
       <c r="E133" t="s">
@@ -3674,18 +3684,18 @@
       <c r="F133" t="s">
         <v>135</v>
       </c>
-      <c r="G133" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G133" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="18" t="s">
         <v>154</v>
       </c>
       <c r="B134" s="15">
         <v>1.05263157894737E-9</v>
       </c>
-      <c r="C134" s="24" t="s">
+      <c r="C134" t="s">
         <v>30</v>
       </c>
       <c r="E134" t="s">
@@ -3694,18 +3704,18 @@
       <c r="F134" t="s">
         <v>135</v>
       </c>
-      <c r="G134" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G134" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="18" t="s">
         <v>155</v>
       </c>
       <c r="B135" s="15">
         <v>1.5789473684210501E-7</v>
       </c>
-      <c r="C135" s="24" t="s">
+      <c r="C135" t="s">
         <v>30</v>
       </c>
       <c r="E135" t="s">
@@ -3714,18 +3724,18 @@
       <c r="F135" t="s">
         <v>135</v>
       </c>
-      <c r="G135" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G135" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="18" t="s">
         <v>156</v>
       </c>
       <c r="B136" s="15">
         <v>4.2105263157894802E-7</v>
       </c>
-      <c r="C136" s="24" t="s">
+      <c r="C136" t="s">
         <v>30</v>
       </c>
       <c r="E136" t="s">
@@ -3734,18 +3744,18 @@
       <c r="F136" t="s">
         <v>135</v>
       </c>
-      <c r="G136" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G136" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="18" t="s">
         <v>95</v>
       </c>
       <c r="B137" s="15">
         <v>1.0526315789473699E-11</v>
       </c>
-      <c r="C137" s="24" t="s">
+      <c r="C137" t="s">
         <v>30</v>
       </c>
       <c r="E137" t="s">
@@ -3754,18 +3764,18 @@
       <c r="F137" t="s">
         <v>135</v>
       </c>
-      <c r="G137" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G137" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="18" t="s">
         <v>157</v>
       </c>
       <c r="B138" s="15">
         <v>7.3684210526315899E-7</v>
       </c>
-      <c r="C138" s="24" t="s">
+      <c r="C138" t="s">
         <v>30</v>
       </c>
       <c r="E138" t="s">
@@ -3774,18 +3784,18 @@
       <c r="F138" t="s">
         <v>135</v>
       </c>
-      <c r="G138" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G138" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="18" t="s">
         <v>158</v>
       </c>
       <c r="B139" s="15">
         <v>0</v>
       </c>
-      <c r="C139" s="24" t="s">
+      <c r="C139" t="s">
         <v>30</v>
       </c>
       <c r="E139" t="s">
@@ -3794,18 +3804,18 @@
       <c r="F139" t="s">
         <v>135</v>
       </c>
-      <c r="G139" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G139" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="18" t="s">
         <v>144</v>
       </c>
       <c r="B140" s="15">
         <v>1.05263157894737E-7</v>
       </c>
-      <c r="C140" s="24" t="s">
+      <c r="C140" t="s">
         <v>30</v>
       </c>
       <c r="E140" t="s">
@@ -3814,18 +3824,18 @@
       <c r="F140" t="s">
         <v>135</v>
       </c>
-      <c r="G140" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G140" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
         <v>94</v>
       </c>
       <c r="B141" s="15">
         <v>3.1578947368421103E-11</v>
       </c>
-      <c r="C141" s="24" t="s">
+      <c r="C141" t="s">
         <v>30</v>
       </c>
       <c r="E141" t="s">
@@ -3834,18 +3844,18 @@
       <c r="F141" t="s">
         <v>135</v>
       </c>
-      <c r="G141" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G141" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="18" t="s">
         <v>159</v>
       </c>
       <c r="B142" s="15">
         <v>1.0526315789473701E-8</v>
       </c>
-      <c r="C142" s="24" t="s">
+      <c r="C142" t="s">
         <v>30</v>
       </c>
       <c r="E142" t="s">
@@ -3854,18 +3864,18 @@
       <c r="F142" t="s">
         <v>135</v>
       </c>
-      <c r="G142" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G142" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="18" t="s">
         <v>160</v>
       </c>
       <c r="B143" s="15">
         <v>1.2631578947368401E-6</v>
       </c>
-      <c r="C143" s="24" t="s">
+      <c r="C143" t="s">
         <v>30</v>
       </c>
       <c r="E143" t="s">
@@ -3874,18 +3884,18 @@
       <c r="F143" t="s">
         <v>135</v>
       </c>
-      <c r="G143" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G143" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="18" t="s">
         <v>161</v>
       </c>
       <c r="B144" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C144" s="24" t="s">
+      <c r="C144" t="s">
         <v>30</v>
       </c>
       <c r="E144" t="s">
@@ -3894,18 +3904,18 @@
       <c r="F144" t="s">
         <v>135</v>
       </c>
-      <c r="G144" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G144" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="18" t="s">
         <v>162</v>
       </c>
       <c r="B145" s="15">
         <v>2.1052631578947401E-8</v>
       </c>
-      <c r="C145" s="24" t="s">
+      <c r="C145" t="s">
         <v>30</v>
       </c>
       <c r="E145" t="s">
@@ -3914,18 +3924,18 @@
       <c r="F145" t="s">
         <v>135</v>
       </c>
-      <c r="G145" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G145" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="18" t="s">
         <v>163</v>
       </c>
       <c r="B146" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C146" s="24" t="s">
+      <c r="C146" t="s">
         <v>30</v>
       </c>
       <c r="E146" t="s">
@@ -3934,11 +3944,11 @@
       <c r="F146" t="s">
         <v>135</v>
       </c>
-      <c r="G146" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G146" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3"/>
@@ -3948,7 +3958,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>0</v>
       </c>
@@ -3962,7 +3972,7 @@
       <c r="G148" s="8"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>2</v>
       </c>
@@ -3976,7 +3986,7 @@
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>3</v>
       </c>
@@ -3990,7 +4000,7 @@
       <c r="G150" s="8"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>5</v>
       </c>
@@ -4004,7 +4014,7 @@
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>6</v>
       </c>
@@ -4018,7 +4028,7 @@
       <c r="G152" s="8"/>
       <c r="H152" s="8"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>8</v>
       </c>
@@ -4032,7 +4042,7 @@
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>10</v>
       </c>
@@ -4044,7 +4054,7 @@
       <c r="G154" s="8"/>
       <c r="H154" s="8"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>11</v>
       </c>
@@ -4070,7 +4080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>40</v>
       </c>
@@ -4094,7 +4104,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
         <v>116</v>
       </c>
@@ -4118,7 +4128,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
         <v>32</v>
       </c>
@@ -4140,7 +4150,7 @@
       </c>
       <c r="H158" s="8"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>38</v>
       </c>
@@ -4172,15 +4182,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4866E389-DAB9-471E-90B6-60D41E2985DE}">
   <dimension ref="A1:AH150"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="97.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.5" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -4220,7 +4230,7 @@
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
@@ -4260,7 +4270,7 @@
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>3</v>
       </c>
@@ -4300,7 +4310,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -4340,7 +4350,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>5</v>
       </c>
@@ -4380,7 +4390,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
         <v>8</v>
       </c>
@@ -4420,7 +4430,7 @@
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>148</v>
       </c>
@@ -4460,7 +4470,7 @@
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>10</v>
       </c>
@@ -4498,14 +4508,14 @@
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="19" t="s">
@@ -4550,14 +4560,14 @@
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>192</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -4600,14 +4610,14 @@
       <c r="AG10" s="5"/>
       <c r="AH10" s="5"/>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>195</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -4650,14 +4660,14 @@
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>196</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>0.38400000000000001</v>
       </c>
       <c r="D12" t="s">
@@ -4699,14 +4709,14 @@
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <v>2.8400000000000002E-4</v>
       </c>
       <c r="D13" t="s">
@@ -4748,14 +4758,14 @@
       <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <v>3.0400000000000002E-4</v>
       </c>
       <c r="D14" t="s">
@@ -4797,14 +4807,14 @@
       <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>175</v>
       </c>
       <c r="B15" t="s">
         <v>176</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <v>8.2600000000000002E-5</v>
       </c>
       <c r="D15" t="s">
@@ -4846,14 +4856,14 @@
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>171</v>
       </c>
       <c r="B16" t="s">
         <v>172</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <v>8.2699999999999996E-11</v>
       </c>
       <c r="D16" t="s">
@@ -4895,14 +4905,14 @@
       <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>173</v>
       </c>
       <c r="B17" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <v>7.4400000000000002E-10</v>
       </c>
       <c r="D17" t="s">
@@ -4944,14 +4954,14 @@
       <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>177</v>
       </c>
       <c r="B18" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <v>3.3099999999999999E-10</v>
       </c>
       <c r="D18" t="s">
@@ -4993,14 +5003,14 @@
       <c r="AG18" s="5"/>
       <c r="AH18" s="5"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>179</v>
       </c>
       <c r="B19" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <v>5.1400000000000003E-12</v>
       </c>
       <c r="D19" t="s">
@@ -5042,14 +5052,14 @@
       <c r="AG19" s="5"/>
       <c r="AH19" s="5"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>181</v>
       </c>
       <c r="B20" t="s">
         <v>182</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <v>5.7899999999999997E-10</v>
       </c>
       <c r="D20" t="s">
@@ -5091,14 +5101,14 @@
       <c r="AG20" s="5"/>
       <c r="AH20" s="5"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <v>-2.2699999999999999E-4</v>
       </c>
       <c r="D21" t="s">
@@ -5140,7 +5150,7 @@
       <c r="AG21" s="5"/>
       <c r="AH21" s="5"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
         <v>32</v>
       </c>
@@ -5187,11 +5197,11 @@
       <c r="AG22" s="5"/>
       <c r="AH22" s="5"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <v>1.2300000000000001E-4</v>
       </c>
       <c r="D23" t="s">
@@ -5233,7 +5243,7 @@
       <c r="AG23" s="5"/>
       <c r="AH23" s="5"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" s="17" t="s">
         <v>88</v>
       </c>
@@ -5280,7 +5290,7 @@
       <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
@@ -5316,7 +5326,7 @@
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>0</v>
       </c>
@@ -5330,7 +5340,7 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>2</v>
       </c>
@@ -5344,7 +5354,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
         <v>3</v>
       </c>
@@ -5358,7 +5368,7 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
@@ -5372,7 +5382,7 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>5</v>
       </c>
@@ -5386,7 +5396,7 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
         <v>8</v>
       </c>
@@ -5400,7 +5410,7 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
         <v>148</v>
       </c>
@@ -5414,7 +5424,7 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
         <v>10</v>
       </c>
@@ -5426,14 +5436,14 @@
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="19" t="s">
@@ -5452,14 +5462,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>195</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="25">
         <v>1</v>
       </c>
       <c r="D35" s="5" t="s">
@@ -5476,14 +5486,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
         <v>196</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="26">
         <v>9.4800000000000006E-3</v>
       </c>
       <c r="D36" t="s">
@@ -5499,7 +5509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>177</v>
       </c>
@@ -5522,14 +5532,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>201</v>
       </c>
       <c r="B38" t="s">
         <v>201</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="27">
         <v>1.25334E-10</v>
       </c>
       <c r="D38" t="s">
@@ -5545,7 +5555,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -5568,7 +5578,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="3"/>
@@ -5578,7 +5588,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="19" t="s">
         <v>0</v>
       </c>
@@ -5592,7 +5602,7 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="19" t="s">
         <v>2</v>
       </c>
@@ -5606,7 +5616,7 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>3</v>
       </c>
@@ -5620,7 +5630,7 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -5634,7 +5644,7 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
         <v>5</v>
       </c>
@@ -5648,7 +5658,7 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="19" t="s">
         <v>8</v>
       </c>
@@ -5662,7 +5672,7 @@
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="19" t="s">
         <v>148</v>
       </c>
@@ -5676,7 +5686,7 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="19" t="s">
         <v>10</v>
       </c>
@@ -5688,14 +5698,14 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="19" t="s">
@@ -5714,14 +5724,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="17" t="s">
         <v>201</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C50" s="26">
+      <c r="C50" s="25">
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -5738,7 +5748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -5761,7 +5771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>205</v>
       </c>
@@ -5784,7 +5794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>207</v>
       </c>
@@ -5807,7 +5817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>208</v>
       </c>
@@ -5830,7 +5840,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>209</v>
       </c>
@@ -5853,7 +5863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>211</v>
       </c>
@@ -5876,7 +5886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>213</v>
       </c>
@@ -5899,7 +5909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>215</v>
       </c>
@@ -5922,7 +5932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>217</v>
       </c>
@@ -5945,7 +5955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>109</v>
       </c>
@@ -5968,7 +5978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>218</v>
       </c>
@@ -5991,7 +6001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>220</v>
       </c>
@@ -6014,7 +6024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -6034,7 +6044,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>101</v>
       </c>
@@ -6054,7 +6064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>103</v>
       </c>
@@ -6074,7 +6084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>222</v>
       </c>
@@ -6094,7 +6104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="3"/>
@@ -6104,7 +6114,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="19" t="s">
         <v>0</v>
       </c>
@@ -6118,7 +6128,7 @@
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="19" t="s">
         <v>2</v>
       </c>
@@ -6132,7 +6142,7 @@
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="19" t="s">
         <v>3</v>
       </c>
@@ -6146,7 +6156,7 @@
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -6160,7 +6170,7 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="19" t="s">
         <v>5</v>
       </c>
@@ -6174,7 +6184,7 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="19" t="s">
         <v>8</v>
       </c>
@@ -6188,7 +6198,7 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="19" t="s">
         <v>148</v>
       </c>
@@ -6202,7 +6212,7 @@
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="19" t="s">
         <v>10</v>
       </c>
@@ -6214,14 +6224,14 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C76" s="25" t="s">
+      <c r="C76" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="19" t="s">
@@ -6240,14 +6250,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>203</v>
       </c>
       <c r="B77" t="s">
         <v>203</v>
       </c>
-      <c r="C77" s="26">
+      <c r="C77" s="25">
         <v>1</v>
       </c>
       <c r="D77" s="5" t="s">
@@ -6264,7 +6274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>224</v>
       </c>
@@ -6288,7 +6298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>226</v>
       </c>
@@ -6312,7 +6322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>228</v>
       </c>
@@ -6336,7 +6346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>230</v>
       </c>
@@ -6360,7 +6370,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>231</v>
       </c>
@@ -6384,7 +6394,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>233</v>
       </c>
@@ -6408,7 +6418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>235</v>
       </c>
@@ -6432,7 +6442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>237</v>
       </c>
@@ -6456,7 +6466,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>208</v>
       </c>
@@ -6480,7 +6490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>211</v>
       </c>
@@ -6504,7 +6514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>213</v>
       </c>
@@ -6528,7 +6538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>239</v>
       </c>
@@ -6552,7 +6562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>241</v>
       </c>
@@ -6576,7 +6586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>242</v>
       </c>
@@ -6600,7 +6610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>140</v>
       </c>
@@ -6622,7 +6632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>254</v>
       </c>
@@ -6644,7 +6654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>255</v>
       </c>
@@ -6666,7 +6676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>137</v>
       </c>
@@ -6688,7 +6698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>256</v>
       </c>
@@ -6710,7 +6720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>244</v>
       </c>
@@ -6732,7 +6742,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>146</v>
       </c>
@@ -6754,7 +6764,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>260</v>
       </c>
@@ -6776,7 +6786,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>136</v>
       </c>
@@ -6798,7 +6808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>261</v>
       </c>
@@ -6820,7 +6830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>142</v>
       </c>
@@ -6842,7 +6852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>245</v>
       </c>
@@ -6864,7 +6874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>246</v>
       </c>
@@ -6886,7 +6896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>257</v>
       </c>
@@ -6908,7 +6918,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>247</v>
       </c>
@@ -6930,7 +6940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>258</v>
       </c>
@@ -6952,7 +6962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>248</v>
       </c>
@@ -6974,7 +6984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>259</v>
       </c>
@@ -6996,7 +7006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>145</v>
       </c>
@@ -7018,7 +7028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>262</v>
       </c>
@@ -7040,7 +7050,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>249</v>
       </c>
@@ -7062,7 +7072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>263</v>
       </c>
@@ -7084,7 +7094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>250</v>
       </c>
@@ -7106,7 +7116,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>251</v>
       </c>
@@ -7128,7 +7138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>139</v>
       </c>
@@ -7150,7 +7160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>252</v>
       </c>
@@ -7172,7 +7182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>264</v>
       </c>
@@ -7194,100 +7204,100 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C119" s="16"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C120" s="16"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C121" s="16"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C122" s="16"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C123" s="16"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C124" s="16"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C125" s="16"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C126" s="16"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C127" s="16"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C128" s="16"/>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C129" s="16"/>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C130" s="16"/>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C131" s="16"/>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C132" s="16"/>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C133" s="16"/>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C134" s="16"/>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C135" s="16"/>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C136" s="16"/>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C137" s="16"/>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C138" s="16"/>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C139" s="16"/>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C140" s="16"/>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C141" s="16"/>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C142" s="16"/>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C143" s="16"/>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C144" s="16"/>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C145" s="16"/>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C146" s="16"/>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C147" s="16"/>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C148" s="16"/>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C149" s="16"/>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C150" s="16"/>
     </row>
   </sheetData>
@@ -7298,17 +7308,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H81"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="94.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7322,7 +7332,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -7336,7 +7346,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -7350,7 +7360,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -7364,7 +7374,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -7378,7 +7388,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -7392,7 +7402,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -7404,7 +7414,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -7430,7 +7440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -7454,7 +7464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7478,7 +7488,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -7502,7 +7512,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -7525,7 +7535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>128</v>
       </c>
@@ -7549,7 +7559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>183</v>
       </c>
@@ -7572,7 +7582,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>184</v>
       </c>
@@ -7596,7 +7606,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -7619,7 +7629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>186</v>
       </c>
@@ -7642,7 +7652,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7662,7 +7672,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7682,7 +7692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -7703,7 +7713,7 @@
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7724,7 +7734,7 @@
       </c>
       <c r="H21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7744,7 +7754,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7764,7 +7774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -7774,7 +7784,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,7 +7798,7 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
@@ -7802,7 +7812,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -7816,7 +7826,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
@@ -7830,7 +7840,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
@@ -7844,7 +7854,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -7858,7 +7868,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -7870,7 +7880,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
@@ -7896,7 +7906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -7920,7 +7930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -7944,7 +7954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>133</v>
       </c>
@@ -7968,7 +7978,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
         <v>192</v>
       </c>
@@ -7993,7 +8003,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -8017,7 +8027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>128</v>
       </c>
@@ -8041,7 +8051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>183</v>
       </c>
@@ -8064,7 +8074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -8088,7 +8098,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -8111,7 +8121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
         <v>186</v>
       </c>
@@ -8134,7 +8144,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -8154,7 +8164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -8174,7 +8184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -8195,7 +8205,7 @@
       </c>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -8217,7 +8227,7 @@
       </c>
       <c r="H46" s="14"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -8237,7 +8247,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -8257,7 +8267,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3"/>
@@ -8267,7 +8277,7 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>0</v>
       </c>
@@ -8281,7 +8291,7 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>2</v>
       </c>
@@ -8295,7 +8305,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>3</v>
       </c>
@@ -8309,7 +8319,7 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>5</v>
       </c>
@@ -8323,7 +8333,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>6</v>
       </c>
@@ -8337,7 +8347,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>8</v>
       </c>
@@ -8351,7 +8361,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>10</v>
       </c>
@@ -8363,7 +8373,7 @@
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>11</v>
       </c>
@@ -8389,7 +8399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>119</v>
       </c>
@@ -8413,7 +8423,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>40</v>
       </c>
@@ -8437,7 +8447,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -8461,7 +8471,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -8485,7 +8495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -8505,7 +8515,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>54</v>
       </c>
@@ -8528,7 +8538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>34</v>
       </c>
@@ -8548,7 +8558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>35</v>
       </c>
@@ -8568,7 +8578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>37</v>
       </c>
@@ -8588,7 +8598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -8609,7 +8619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -8630,7 +8640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>109</v>
       </c>
@@ -8653,41 +8663,40 @@
         <v>110</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="24"/>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B73" s="15"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B74" s="4"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B80" s="15"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="8"/>
       <c r="B81" s="13"/>
       <c r="C81" s="8"/>
@@ -8705,17 +8714,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8729,7 +8738,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8743,7 +8752,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8757,7 +8766,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8771,7 +8780,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8785,7 +8794,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8799,7 +8808,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8811,7 +8820,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8837,7 +8846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>120</v>
       </c>
@@ -8861,7 +8870,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8885,7 +8894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -8909,7 +8918,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -8932,7 +8941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>124</v>
       </c>
@@ -8956,7 +8965,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -8980,7 +8989,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -9004,7 +9013,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -9028,7 +9037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -9052,7 +9061,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>129</v>
       </c>
@@ -9077,7 +9086,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -9100,7 +9109,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -9120,7 +9129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -9140,7 +9149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>136</v>
       </c>
@@ -9160,7 +9169,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -9180,7 +9189,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -9200,7 +9209,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -9220,7 +9229,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -9240,7 +9249,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -9260,7 +9269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>140</v>
       </c>
@@ -9280,7 +9289,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>138</v>
       </c>
@@ -9300,7 +9309,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -9320,7 +9329,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>141</v>
       </c>
@@ -9340,7 +9349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>142</v>
       </c>
@@ -9360,7 +9369,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -9380,7 +9389,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>144</v>
       </c>
@@ -9400,7 +9409,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>145</v>
       </c>
@@ -9420,7 +9429,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>146</v>
       </c>
@@ -9441,7 +9450,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>147</v>
       </c>
@@ -9463,7 +9472,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9473,7 +9482,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9487,7 +9496,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
@@ -9501,7 +9510,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9515,7 +9524,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9529,7 +9538,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9543,7 +9552,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9557,7 +9566,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9569,7 +9578,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9595,7 +9604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>123</v>
       </c>
@@ -9619,7 +9628,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9643,7 +9652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="17" t="s">
         <v>133</v>
       </c>
@@ -9667,7 +9676,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -9691,7 +9700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>124</v>
       </c>
@@ -9715,7 +9724,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -9739,7 +9748,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -9763,7 +9772,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>128</v>
       </c>
@@ -9787,7 +9796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>48</v>
       </c>
@@ -9811,7 +9820,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>129</v>
       </c>
@@ -9836,7 +9845,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>130</v>
       </c>
@@ -9859,7 +9868,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -9879,7 +9888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9899,7 +9908,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>136</v>
       </c>
@@ -9919,7 +9928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9939,7 +9948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9959,7 +9968,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>137</v>
       </c>
@@ -9979,7 +9988,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>138</v>
       </c>
@@ -9999,7 +10008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>139</v>
       </c>
@@ -10019,7 +10028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>140</v>
       </c>
@@ -10039,7 +10048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -10059,7 +10068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -10079,7 +10088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>141</v>
       </c>
@@ -10099,7 +10108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>142</v>
       </c>
@@ -10119,7 +10128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>143</v>
       </c>
@@ -10139,7 +10148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>144</v>
       </c>
@@ -10159,7 +10168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -10179,7 +10188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>146</v>
       </c>
@@ -10200,7 +10209,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>147</v>
       </c>
@@ -10231,18 +10240,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10250,7 +10259,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -10258,7 +10267,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -10266,7 +10275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -10274,7 +10283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -10282,7 +10291,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -10290,12 +10299,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10321,7 +10330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>170</v>
       </c>
@@ -10344,7 +10353,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>120</v>
       </c>
@@ -10367,7 +10376,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -10391,7 +10400,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10413,7 +10422,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>167</v>
       </c>
@@ -10436,7 +10445,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -10459,7 +10468,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10479,7 +10488,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -10499,7 +10508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>169</v>
       </c>
@@ -10522,7 +10531,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>88</v>
       </c>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF93657-23D2-B240-B91E-134D555924B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47F7E86-A444-DC40-83A7-6F3A803B014F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
-    <sheet name="Carbon dioxide capture" sheetId="9" r:id="rId2"/>
-    <sheet name="Ammonia" sheetId="5" r:id="rId3"/>
-    <sheet name="Methanol" sheetId="7" r:id="rId4"/>
-    <sheet name="Ethylene" sheetId="8" r:id="rId5"/>
+    <sheet name="Ammonia" sheetId="5" r:id="rId2"/>
+    <sheet name="Methanol" sheetId="7" r:id="rId3"/>
+    <sheet name="Ethylene" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="165">
   <si>
     <t>Activity</t>
   </si>
@@ -300,21 +299,9 @@
     <t>monoethanolamine</t>
   </si>
   <si>
-    <t>market for sodium hydroxide, without water, in 50% solution state</t>
-  </si>
-  <si>
-    <t>sodium hydroxide, without water, in 50% solution state</t>
-  </si>
-  <si>
     <t>Monoethanolamine</t>
   </si>
   <si>
-    <t>treatment of spent solvent mixture, hazardous waste incineration</t>
-  </si>
-  <si>
-    <t>spent solvent mixture</t>
-  </si>
-  <si>
     <t>Methane, fossil</t>
   </si>
   <si>
@@ -336,39 +323,6 @@
     <t>wastewater, average</t>
   </si>
   <si>
-    <t>Occupation, construction site</t>
-  </si>
-  <si>
-    <t>square meter-year</t>
-  </si>
-  <si>
-    <t>natural resource::land</t>
-  </si>
-  <si>
-    <t>Transformation, from forest, unspecified</t>
-  </si>
-  <si>
-    <t>square meter</t>
-  </si>
-  <si>
-    <t>Transformation, to heterogeneous, agricultural</t>
-  </si>
-  <si>
-    <t>diesel, burned in building machine</t>
-  </si>
-  <si>
-    <t>drawing of pipe, steel</t>
-  </si>
-  <si>
-    <t>ton kilometer</t>
-  </si>
-  <si>
-    <t>meter</t>
-  </si>
-  <si>
-    <t>steel, low-alloyed</t>
-  </si>
-  <si>
     <t>treatment of inert waste, inert material landfill</t>
   </si>
   <si>
@@ -486,9 +440,6 @@
     <t>Phenol</t>
   </si>
   <si>
-    <t>source</t>
-  </si>
-  <si>
     <t>market group for electricity, low voltage</t>
   </si>
   <si>
@@ -555,42 +506,6 @@
     <t>ethylene, MTO; methanol, BAU</t>
   </si>
   <si>
-    <t>heat pump production, heat and power co-generation unit, 160kW electrical</t>
-  </si>
-  <si>
-    <t>heat pump, heat and power co-generation unit, 160kW electrical</t>
-  </si>
-  <si>
-    <t>market for absorption chiller, 100kW</t>
-  </si>
-  <si>
-    <t>absorption chiller, 100kW</t>
-  </si>
-  <si>
-    <t>market for charcoal</t>
-  </si>
-  <si>
-    <t>charcoal</t>
-  </si>
-  <si>
-    <t>market for gas turbine, 10MW electrical</t>
-  </si>
-  <si>
-    <t>gas turbine, 10MW electrical</t>
-  </si>
-  <si>
-    <t>market for liquid storage tank, chemicals, organics</t>
-  </si>
-  <si>
-    <t>liquid storage tank, chemicals, organics</t>
-  </si>
-  <si>
-    <t>market for pump, 40W</t>
-  </si>
-  <si>
-    <t>pump, 40W</t>
-  </si>
-  <si>
     <t>market for tap water</t>
   </si>
   <si>
@@ -618,232 +533,15 @@
     <t>This is the activity for 1 kg of BAU ammonia with CCS</t>
   </si>
   <si>
-    <t>carbon dioxide capture, chemical absorption, with transport and storage, 200 km pipeline sotage 1000m</t>
-  </si>
-  <si>
-    <t>This is the activity for post-combustion CO2 capture using chemical absorption with monoethanolamine (MEA).The electricity consumption includes the compresison of CO2 to 110 bar for pipeline transport. Inventory for transport and injection in a saline aquifer included as input.</t>
-  </si>
-  <si>
-    <t>Volkart et al. (2013): Life cycle assessment of carbon capture and storage in power generation and industry in Europe. International Journal of Greenhouse Gas Control 16, 91–106</t>
-  </si>
-  <si>
-    <t>carbon dioxide transport and storage, 200 km pipeline, storage 1000m</t>
-  </si>
-  <si>
-    <t>market group for electricity, medium voltage</t>
-  </si>
-  <si>
-    <t>electricity, medium voltage</t>
-  </si>
-  <si>
-    <t>This is the activity for the transport and injection of CO2 in a saline aquifer. The pipeline is assumed to have a length of 200 km. Supercritical conditions are required to safely and permanently store CO2 in geological storage sites, that are achieved at a minimum depth of 1000 m. CO2 leakage during transport was considered negligible and omitted. Further details can be found in Volkart et al. (2013): Life cycle assessment of carbon capture and storage in power generation and industry in Europe. International Journal of Greenhouse Gas Control 16, 91–106</t>
-  </si>
-  <si>
-    <t>Inventory from CARMA database as implemented by Antonini et al. (2020): Hydrogen production from natural gas and biomethane with carbon capture and storage – A techno-environmental analysis. Sustainable Energy Fuels, 4, 2967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gas turbine, 10MW electrical </t>
-  </si>
-  <si>
-    <t>pipeline for carbon dioxide transport, supercritical, 200km w/o recompression</t>
-  </si>
-  <si>
-    <t>kilometer</t>
-  </si>
-  <si>
-    <t>drilling, deep borehole/m</t>
-  </si>
-  <si>
-    <t>This is the activity for the infrastructure-related inventory for 1 km of pipeline for carbon dioxide transport. Further details can be found in Volkart et al. (2013): Life cycle assessment of carbon capture and storage in power generation and industry in Europe. International Journal of Greenhouse Gas Control 16, 91–106</t>
-  </si>
-  <si>
-    <t>gravel and sand quarry operation</t>
-  </si>
-  <si>
-    <t>sand</t>
-  </si>
-  <si>
-    <t>market for diesel, burned in building machine</t>
-  </si>
-  <si>
-    <t>market for steel, low-alloyed</t>
-  </si>
-  <si>
-    <t>market for stone wool, packed</t>
-  </si>
-  <si>
-    <t>stone wool, packed</t>
-  </si>
-  <si>
-    <t>market for transport, freight train</t>
-  </si>
-  <si>
-    <t>transport, freight train</t>
-  </si>
-  <si>
-    <t>market for transport, freight, lorry, unspecified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transport, freight, lorry, unspecified </t>
-  </si>
-  <si>
-    <t>transport, helicopter</t>
-  </si>
-  <si>
-    <t>hour</t>
-  </si>
-  <si>
-    <t>transport, helicopter, LTO cycle</t>
-  </si>
-  <si>
-    <t>treatment of scrap steel, inert material landfill</t>
-  </si>
-  <si>
-    <t>scrap steel</t>
-  </si>
-  <si>
-    <t>treatment of waste mineral wool, inert material landfill</t>
-  </si>
-  <si>
-    <t>waste mineral wool, for final disposal</t>
-  </si>
-  <si>
-    <t>Water, unspecified natural origin</t>
-  </si>
-  <si>
-    <t>This is the activity for the infrastructure-related inventory for 1 meter of drilling. Further details can be found in Volkart et al. (2013): Life cycle assessment of carbon capture and storage in power generation and industry in Europe. International Journal of Greenhouse Gas Control 16, 91–106</t>
-  </si>
-  <si>
-    <t>activated bentonite production</t>
-  </si>
-  <si>
-    <t>activated bentonite</t>
-  </si>
-  <si>
-    <t>barite production</t>
-  </si>
-  <si>
-    <t>barite</t>
-  </si>
-  <si>
-    <t>cement production, Portland</t>
-  </si>
-  <si>
-    <t>cement, Portland</t>
-  </si>
-  <si>
-    <t>diesel, burned in diesel-electric generating set, 18.5kW</t>
-  </si>
-  <si>
-    <t>lignite mine operation</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>market for chemical, organic</t>
-  </si>
-  <si>
-    <t>chemical, organic</t>
-  </si>
-  <si>
-    <t>market for chemical, inorganic</t>
-  </si>
-  <si>
-    <t>chemical, inorganic</t>
-  </si>
-  <si>
-    <t>market for lubricating oil</t>
-  </si>
-  <si>
-    <t>lubricating oil</t>
-  </si>
-  <si>
-    <t>treatment of drilling waste, landfarming</t>
-  </si>
-  <si>
-    <t>drilling waste</t>
-  </si>
-  <si>
-    <t>treatment of drilling waste, residual material landfill</t>
-  </si>
-  <si>
-    <t>treatment of hazardous waste, hazardous waste incineration</t>
-  </si>
-  <si>
-    <t>hazardous waste, for incineration</t>
-  </si>
-  <si>
-    <t>Boron</t>
-  </si>
-  <si>
-    <t>Fluoride</t>
-  </si>
-  <si>
-    <t>Hydrocarbons, aromatic</t>
-  </si>
-  <si>
-    <t>Magnesium</t>
-  </si>
-  <si>
-    <t>Methane, dichloro-, HCC-30</t>
-  </si>
-  <si>
-    <t>Silicon</t>
-  </si>
-  <si>
-    <t>Strontium</t>
-  </si>
-  <si>
-    <t>Sulfur</t>
-  </si>
-  <si>
-    <t>Water, well, in ground</t>
-  </si>
-  <si>
     <t>market group for natural gas, high pressure</t>
-  </si>
-  <si>
-    <t>Aluminium</t>
-  </si>
-  <si>
-    <t>Arsenic, ion</t>
-  </si>
-  <si>
-    <t>Barium</t>
-  </si>
-  <si>
-    <t>Iron, ion</t>
-  </si>
-  <si>
-    <t>Manganese</t>
-  </si>
-  <si>
-    <t>Particulates, &gt; 10 um</t>
-  </si>
-  <si>
-    <t>Calcium, ion</t>
-  </si>
-  <si>
-    <t>Chromium, ion</t>
-  </si>
-  <si>
-    <t>Potassium, ion</t>
-  </si>
-  <si>
-    <t>Sodium, ion</t>
-  </si>
-  <si>
-    <t>Zinc, ion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -915,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -955,27 +653,10 @@
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1293,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
@@ -1746,7 +1427,7 @@
         <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -2244,7 +1925,7 @@
         <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2470,7 +2151,7 @@
         <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -2720,7 +2401,7 @@
         <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -2946,7 +2627,7 @@
         <v>20</v>
       </c>
       <c r="H94" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -2987,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
@@ -3043,7 +2724,7 @@
         <v>6</v>
       </c>
       <c r="B101" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
@@ -3106,7 +2787,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B105" s="9">
         <v>1</v>
@@ -3125,7 +2806,7 @@
         <v>17</v>
       </c>
       <c r="H105" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -3311,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
@@ -3367,7 +3048,7 @@
         <v>6</v>
       </c>
       <c r="B118" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
@@ -3430,7 +3111,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="17" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B122" s="9">
         <v>1</v>
@@ -3449,12 +3130,12 @@
         <v>17</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>253</v>
+        <v>164</v>
       </c>
       <c r="B123" s="9">
         <v>2.8998115122517001E-2</v>
@@ -3478,10 +3159,11 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="17" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B124" s="9">
-        <v>1.1684210526315801E-3</v>
+        <f>0.00116842105263158+0.146*B126/0.1*0.9</f>
+        <v>8.9140568526315783E-3</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>
@@ -3497,12 +3179,12 @@
         <v>20</v>
       </c>
       <c r="H124" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="17" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="B125" s="15">
         <v>2.9473684210526402E-9</v>
@@ -3521,39 +3203,36 @@
         <v>20</v>
       </c>
       <c r="H125" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="17" t="s">
-        <v>192</v>
+      <c r="A126" t="s">
+        <v>29</v>
       </c>
       <c r="B126" s="9">
-        <v>5.3052631578947428E-2</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D126" s="17" t="s">
-        <v>4</v>
+        <f>0.1*0.058947</f>
+        <v>5.8947000000000001E-3</v>
+      </c>
+      <c r="C126" t="s">
+        <v>30</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
       </c>
-      <c r="F126" s="8"/>
+      <c r="F126" s="8" t="s">
+        <v>120</v>
+      </c>
       <c r="G126" t="s">
-        <v>20</v>
-      </c>
-      <c r="H126" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>29</v>
-      </c>
-      <c r="B127" s="9">
-        <v>5.8947368421052686E-3</v>
+        <v>88</v>
+      </c>
+      <c r="B127" s="15">
+        <v>2.2105263157894801E-6</v>
       </c>
       <c r="C127" t="s">
         <v>30</v>
@@ -3562,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G127" t="s">
         <v>31</v>
@@ -3570,10 +3249,10 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B128" s="15">
-        <v>2.2105263157894801E-6</v>
+        <v>2.10526315789474E-6</v>
       </c>
       <c r="C128" t="s">
         <v>30</v>
@@ -3582,18 +3261,18 @@
         <v>9</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G128" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>91</v>
+      <c r="A129" s="18" t="s">
+        <v>137</v>
       </c>
       <c r="B129" s="15">
-        <v>2.10526315789474E-6</v>
+        <v>1.05263157894737E-7</v>
       </c>
       <c r="C129" t="s">
         <v>30</v>
@@ -3601,19 +3280,19 @@
       <c r="E129" t="s">
         <v>9</v>
       </c>
-      <c r="F129" s="8" t="s">
-        <v>135</v>
+      <c r="F129" t="s">
+        <v>120</v>
       </c>
       <c r="G129" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="18" t="s">
-        <v>153</v>
+      <c r="A130" t="s">
+        <v>37</v>
       </c>
       <c r="B130" s="15">
-        <v>1.05263157894737E-7</v>
+        <v>1.8842105263157901E-5</v>
       </c>
       <c r="C130" t="s">
         <v>30</v>
@@ -3622,18 +3301,18 @@
         <v>9</v>
       </c>
       <c r="F130" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G130" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>37</v>
+      <c r="A131" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="B131" s="15">
-        <v>1.8842105263157901E-5</v>
+        <v>5.7894736842105305E-7</v>
       </c>
       <c r="C131" t="s">
         <v>30</v>
@@ -3642,7 +3321,7 @@
         <v>9</v>
       </c>
       <c r="F131" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G131" t="s">
         <v>31</v>
@@ -3650,10 +3329,10 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="18" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="B132" s="15">
-        <v>5.7894736842105305E-7</v>
+        <v>2.1052631578947401E-7</v>
       </c>
       <c r="C132" t="s">
         <v>30</v>
@@ -3662,7 +3341,7 @@
         <v>9</v>
       </c>
       <c r="F132" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G132" t="s">
         <v>31</v>
@@ -3670,10 +3349,10 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="18" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="B133" s="15">
-        <v>2.1052631578947401E-7</v>
+        <v>1.05263157894737E-9</v>
       </c>
       <c r="C133" t="s">
         <v>30</v>
@@ -3682,7 +3361,7 @@
         <v>9</v>
       </c>
       <c r="F133" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G133" t="s">
         <v>31</v>
@@ -3690,10 +3369,10 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="18" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B134" s="15">
-        <v>1.05263157894737E-9</v>
+        <v>1.5789473684210501E-7</v>
       </c>
       <c r="C134" t="s">
         <v>30</v>
@@ -3702,7 +3381,7 @@
         <v>9</v>
       </c>
       <c r="F134" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G134" t="s">
         <v>31</v>
@@ -3710,10 +3389,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="18" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B135" s="15">
-        <v>1.5789473684210501E-7</v>
+        <v>4.2105263157894802E-7</v>
       </c>
       <c r="C135" t="s">
         <v>30</v>
@@ -3722,7 +3401,7 @@
         <v>9</v>
       </c>
       <c r="F135" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G135" t="s">
         <v>31</v>
@@ -3730,10 +3409,10 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="18" t="s">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="B136" s="15">
-        <v>4.2105263157894802E-7</v>
+        <v>1.0526315789473699E-11</v>
       </c>
       <c r="C136" t="s">
         <v>30</v>
@@ -3742,7 +3421,7 @@
         <v>9</v>
       </c>
       <c r="F136" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G136" t="s">
         <v>31</v>
@@ -3750,10 +3429,10 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="18" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="B137" s="15">
-        <v>1.0526315789473699E-11</v>
+        <v>7.3684210526315899E-7</v>
       </c>
       <c r="C137" t="s">
         <v>30</v>
@@ -3762,7 +3441,7 @@
         <v>9</v>
       </c>
       <c r="F137" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G137" t="s">
         <v>31</v>
@@ -3770,10 +3449,10 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="18" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B138" s="15">
-        <v>7.3684210526315899E-7</v>
+        <v>0</v>
       </c>
       <c r="C138" t="s">
         <v>30</v>
@@ -3782,7 +3461,7 @@
         <v>9</v>
       </c>
       <c r="F138" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G138" t="s">
         <v>31</v>
@@ -3790,10 +3469,10 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="18" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B139" s="15">
-        <v>0</v>
+        <v>1.05263157894737E-7</v>
       </c>
       <c r="C139" t="s">
         <v>30</v>
@@ -3802,18 +3481,18 @@
         <v>9</v>
       </c>
       <c r="F139" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G139" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" s="18" t="s">
-        <v>144</v>
+      <c r="A140" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="B140" s="15">
-        <v>1.05263157894737E-7</v>
+        <v>3.1578947368421103E-11</v>
       </c>
       <c r="C140" t="s">
         <v>30</v>
@@ -3822,18 +3501,18 @@
         <v>9</v>
       </c>
       <c r="F140" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G140" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" s="17" t="s">
-        <v>94</v>
+      <c r="A141" s="18" t="s">
+        <v>143</v>
       </c>
       <c r="B141" s="15">
-        <v>3.1578947368421103E-11</v>
+        <v>1.0526315789473701E-8</v>
       </c>
       <c r="C141" t="s">
         <v>30</v>
@@ -3842,7 +3521,7 @@
         <v>9</v>
       </c>
       <c r="F141" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G141" t="s">
         <v>31</v>
@@ -3850,10 +3529,10 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="18" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B142" s="15">
-        <v>1.0526315789473701E-8</v>
+        <v>1.2631578947368401E-6</v>
       </c>
       <c r="C142" t="s">
         <v>30</v>
@@ -3862,7 +3541,7 @@
         <v>9</v>
       </c>
       <c r="F142" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G142" t="s">
         <v>31</v>
@@ -3870,10 +3549,10 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="18" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B143" s="15">
-        <v>1.2631578947368401E-6</v>
+        <v>2.1052631578947401E-7</v>
       </c>
       <c r="C143" t="s">
         <v>30</v>
@@ -3882,7 +3561,7 @@
         <v>9</v>
       </c>
       <c r="F143" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G143" t="s">
         <v>31</v>
@@ -3890,10 +3569,10 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="18" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B144" s="15">
-        <v>2.1052631578947401E-7</v>
+        <v>2.1052631578947401E-8</v>
       </c>
       <c r="C144" t="s">
         <v>30</v>
@@ -3902,7 +3581,7 @@
         <v>9</v>
       </c>
       <c r="F144" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G144" t="s">
         <v>31</v>
@@ -3910,10 +3589,10 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="18" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B145" s="15">
-        <v>2.1052631578947401E-8</v>
+        <v>2.1052631578947401E-7</v>
       </c>
       <c r="C145" t="s">
         <v>30</v>
@@ -3922,48 +3601,42 @@
         <v>9</v>
       </c>
       <c r="F145" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G145" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A146" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B146" s="15">
-        <v>2.1052631578947401E-7</v>
-      </c>
-      <c r="C146" t="s">
-        <v>30</v>
-      </c>
-      <c r="E146" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" t="s">
-        <v>135</v>
-      </c>
-      <c r="G146" t="s">
-        <v>31</v>
-      </c>
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147" s="2"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-      <c r="H147" s="2"/>
+      <c r="A147" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A148" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>40</v>
+      <c r="A148" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B148" t="s">
+        <v>100</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
@@ -3974,10 +3647,10 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" t="s">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
@@ -3988,10 +3661,10 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B150" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B150" s="8">
+        <v>1</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
@@ -4002,10 +3675,10 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B151" s="8">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B151" t="s">
+        <v>41</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
@@ -4016,10 +3689,10 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B152" t="s">
-        <v>41</v>
+        <v>8</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
@@ -4029,12 +3702,10 @@
       <c r="H152" s="8"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A153" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="A153" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
@@ -4043,97 +3714,108 @@
       <c r="H153" s="8"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="8"/>
-      <c r="G154" s="8"/>
-      <c r="H154" s="8"/>
+      <c r="A154" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B155" s="8" t="s">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="B155" s="9">
+        <v>1</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D155" s="8" t="s">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="D155" t="s">
+        <v>4</v>
       </c>
       <c r="E155" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" s="8"/>
+      <c r="G155" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H155" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A156" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B156" s="6">
+        <v>4.4321789115451698E-10</v>
+      </c>
+      <c r="C156" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F155" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H155" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A156" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B156" s="9">
-        <v>1</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D156" t="s">
-        <v>4</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>9</v>
-      </c>
       <c r="F156" s="8"/>
-      <c r="G156" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H156" t="s">
-        <v>41</v>
+      <c r="G156" t="s">
+        <v>20</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A157" s="5" t="s">
-        <v>116</v>
+      <c r="A157" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B157" s="6">
-        <v>4.4321789115451698E-10</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
-      </c>
-      <c r="D157" t="s">
-        <v>19</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D157" s="8"/>
       <c r="E157" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F157" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="G157" t="s">
-        <v>20</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>117</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H157" s="8"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158" s="7" t="s">
-        <v>32</v>
+      <c r="A158" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="B158" s="6">
-        <v>4.0000000000000001E-3</v>
+        <f>2.45/997</f>
+        <v>2.4573721163490474E-3</v>
       </c>
       <c r="C158" t="s">
         <v>30</v>
@@ -4143,35 +3825,12 @@
         <v>21</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G158" t="s">
         <v>31</v>
       </c>
       <c r="H158" s="8"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B159" s="6">
-        <f>2.45/997</f>
-        <v>2.4573721163490474E-3</v>
-      </c>
-      <c r="C159" t="s">
-        <v>30</v>
-      </c>
-      <c r="D159" s="8"/>
-      <c r="E159" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G159" t="s">
-        <v>31</v>
-      </c>
-      <c r="H159" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4180,3134 +3839,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4866E389-DAB9-471E-90B6-60D41E2985DE}">
-  <dimension ref="A1:AH150"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="97.5" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5"/>
-      <c r="AE5" s="5"/>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
-      <c r="AH6" s="5"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="5"/>
-      <c r="AD7" s="5"/>
-      <c r="AE7" s="5"/>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
-      <c r="AH7" s="5"/>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5"/>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
-      <c r="AH9" s="5"/>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="25">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="25">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="5"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="26">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5"/>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="27">
-        <v>2.8400000000000002E-4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="5"/>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
-      <c r="AH13" s="5"/>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="27">
-        <v>3.0400000000000002E-4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
-      <c r="AB14" s="5"/>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5"/>
-      <c r="AE14" s="5"/>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
-      <c r="AH14" s="5"/>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="27">
-        <v>8.2600000000000002E-5</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
-      <c r="AB15" s="5"/>
-      <c r="AC15" s="5"/>
-      <c r="AD15" s="5"/>
-      <c r="AE15" s="5"/>
-      <c r="AF15" s="5"/>
-      <c r="AG15" s="5"/>
-      <c r="AH15" s="5"/>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="27">
-        <v>8.2699999999999996E-11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5"/>
-      <c r="AA16" s="5"/>
-      <c r="AB16" s="5"/>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="5"/>
-      <c r="AE16" s="5"/>
-      <c r="AF16" s="5"/>
-      <c r="AG16" s="5"/>
-      <c r="AH16" s="5"/>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="27">
-        <v>7.4400000000000002E-10</v>
-      </c>
-      <c r="D17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
-      <c r="AB17" s="5"/>
-      <c r="AC17" s="5"/>
-      <c r="AD17" s="5"/>
-      <c r="AE17" s="5"/>
-      <c r="AF17" s="5"/>
-      <c r="AG17" s="5"/>
-      <c r="AH17" s="5"/>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>177</v>
-      </c>
-      <c r="B18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="27">
-        <v>3.3099999999999999E-10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="5"/>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
-      <c r="AH18" s="5"/>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>179</v>
-      </c>
-      <c r="B19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C19" s="27">
-        <v>5.1400000000000003E-12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
-      <c r="AB19" s="5"/>
-      <c r="AC19" s="5"/>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="5"/>
-      <c r="AF19" s="5"/>
-      <c r="AG19" s="5"/>
-      <c r="AH19" s="5"/>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>181</v>
-      </c>
-      <c r="B20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="27">
-        <v>5.7899999999999997E-10</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="27">
-        <v>-2.2699999999999999E-4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="20">
-        <v>8.3199999999999996E-2</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
-      <c r="AH22" s="5"/>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="27">
-        <v>1.2300000000000001E-4</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="5"/>
-      <c r="AF23" s="5"/>
-      <c r="AG23" s="5"/>
-      <c r="AH23" s="5"/>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="20">
-        <v>6.0000000000000002E-6</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H24" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="5"/>
-      <c r="AF24" s="5"/>
-      <c r="AG24" s="5"/>
-      <c r="AH24" s="5"/>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-      <c r="AD25" s="2"/>
-      <c r="AE25" s="2"/>
-      <c r="AF25" s="2"/>
-      <c r="AG25" s="2"/>
-      <c r="AH25" s="2"/>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A27" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A28" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="7">
-        <v>1</v>
-      </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C35" s="25">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="C36" s="26">
-        <v>9.4800000000000006E-3</v>
-      </c>
-      <c r="D36" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37" t="s">
-        <v>200</v>
-      </c>
-      <c r="C37" s="16">
-        <v>2.5400000000000001E-11</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" t="s">
-        <v>4</v>
-      </c>
-      <c r="H37" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>201</v>
-      </c>
-      <c r="B38" t="s">
-        <v>201</v>
-      </c>
-      <c r="C38" s="27">
-        <v>1.25334E-10</v>
-      </c>
-      <c r="D38" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H38" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" s="16">
-        <v>1.6899999999999999E-8</v>
-      </c>
-      <c r="D39" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H39" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="7">
-        <v>1</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="C50" s="25">
-        <v>1</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="17"/>
-      <c r="G50" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>105</v>
-      </c>
-      <c r="B51" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="16">
-        <v>270000</v>
-      </c>
-      <c r="D51" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>205</v>
-      </c>
-      <c r="B52" t="s">
-        <v>206</v>
-      </c>
-      <c r="C52" s="16">
-        <v>4400000</v>
-      </c>
-      <c r="D52" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>207</v>
-      </c>
-      <c r="B53" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="16">
-        <v>3310000</v>
-      </c>
-      <c r="D53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" t="s">
-        <v>4</v>
-      </c>
-      <c r="H53" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>208</v>
-      </c>
-      <c r="B54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="16">
-        <v>270000</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>209</v>
-      </c>
-      <c r="B55" t="s">
-        <v>210</v>
-      </c>
-      <c r="C55" s="16">
-        <v>5120</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" t="s">
-        <v>4</v>
-      </c>
-      <c r="H55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>211</v>
-      </c>
-      <c r="B56" t="s">
-        <v>212</v>
-      </c>
-      <c r="C56" s="16">
-        <v>55100</v>
-      </c>
-      <c r="D56" t="s">
-        <v>106</v>
-      </c>
-      <c r="E56" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>213</v>
-      </c>
-      <c r="B57" t="s">
-        <v>214</v>
-      </c>
-      <c r="C57" s="16">
-        <v>315000</v>
-      </c>
-      <c r="D57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>215</v>
-      </c>
-      <c r="B58" t="s">
-        <v>215</v>
-      </c>
-      <c r="C58" s="16">
-        <v>26</v>
-      </c>
-      <c r="D58" t="s">
-        <v>216</v>
-      </c>
-      <c r="E58" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>217</v>
-      </c>
-      <c r="B59" t="s">
-        <v>217</v>
-      </c>
-      <c r="C59" s="16">
-        <v>10.4</v>
-      </c>
-      <c r="D59" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>109</v>
-      </c>
-      <c r="B60" t="s">
-        <v>110</v>
-      </c>
-      <c r="C60" s="16">
-        <v>-4400000</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>218</v>
-      </c>
-      <c r="B61" t="s">
-        <v>219</v>
-      </c>
-      <c r="C61" s="16">
-        <v>-135000</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61" t="s">
-        <v>19</v>
-      </c>
-      <c r="H61" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>220</v>
-      </c>
-      <c r="B62" t="s">
-        <v>221</v>
-      </c>
-      <c r="C62" s="16">
-        <v>-5120</v>
-      </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" s="16">
-        <v>3330</v>
-      </c>
-      <c r="D63" t="s">
-        <v>99</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F63" t="s">
-        <v>100</v>
-      </c>
-      <c r="H63" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>101</v>
-      </c>
-      <c r="C64" s="16">
-        <v>2000</v>
-      </c>
-      <c r="D64" t="s">
-        <v>102</v>
-      </c>
-      <c r="E64" t="s">
-        <v>30</v>
-      </c>
-      <c r="F64" t="s">
-        <v>100</v>
-      </c>
-      <c r="H64" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>103</v>
-      </c>
-      <c r="C65" s="16">
-        <v>2000</v>
-      </c>
-      <c r="D65" t="s">
-        <v>102</v>
-      </c>
-      <c r="E65" t="s">
-        <v>30</v>
-      </c>
-      <c r="F65" t="s">
-        <v>100</v>
-      </c>
-      <c r="H65" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>222</v>
-      </c>
-      <c r="C66" s="16">
-        <v>187</v>
-      </c>
-      <c r="D66" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" t="s">
-        <v>30</v>
-      </c>
-      <c r="F66" t="s">
-        <v>33</v>
-      </c>
-      <c r="H66" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C68" s="20"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="C71" s="20"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B72" s="7">
-        <v>1</v>
-      </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C73" s="20"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G76" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>203</v>
-      </c>
-      <c r="B77" t="s">
-        <v>203</v>
-      </c>
-      <c r="C77" s="25">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F77" s="17"/>
-      <c r="G77" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C78" s="5">
-        <v>20</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>18</v>
-      </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C79" s="5">
-        <v>270</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" t="s">
-        <v>18</v>
-      </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C80" s="5">
-        <v>200</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" t="s">
-        <v>18</v>
-      </c>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C81" s="5">
-        <v>6300</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E81" t="s">
-        <v>18</v>
-      </c>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C82" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" t="s">
-        <v>18</v>
-      </c>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C83" s="5">
-        <v>9.0500000000000007</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C84" s="5">
-        <v>42.2</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" t="s">
-        <v>18</v>
-      </c>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C85" s="5">
-        <v>60</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C86" s="5">
-        <v>210</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C87" s="5">
-        <v>487</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E87" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H87" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C88" s="5">
-        <v>81.099999999999994</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E88" t="s">
-        <v>18</v>
-      </c>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C89" s="5">
-        <v>-237</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" t="s">
-        <v>18</v>
-      </c>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C90" s="5">
-        <v>-158</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" t="s">
-        <v>18</v>
-      </c>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C91" s="5">
-        <v>-5</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" t="s">
-        <v>18</v>
-      </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5">
-        <v>4.7800000000000002E-7</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5">
-        <v>3</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5">
-        <v>6</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G107" s="5"/>
-      <c r="H107" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G111" s="5"/>
-      <c r="H111" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5">
-        <v>6</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G113" s="5"/>
-      <c r="H113" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5">
-        <v>3.34</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C119" s="16"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C120" s="16"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C121" s="16"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C122" s="16"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C123" s="16"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C124" s="16"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C125" s="16"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C126" s="16"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C127" s="16"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C128" s="16"/>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C129" s="16"/>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C130" s="16"/>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C131" s="16"/>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C132" s="16"/>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C133" s="16"/>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C134" s="16"/>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C135" s="16"/>
-    </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C136" s="16"/>
-    </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C137" s="16"/>
-    </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C138" s="16"/>
-    </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C139" s="16"/>
-    </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C140" s="16"/>
-    </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C141" s="16"/>
-    </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C142" s="16"/>
-    </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C143" s="16"/>
-    </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C144" s="16"/>
-    </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C145" s="16"/>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C146" s="16"/>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C147" s="16"/>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C148" s="16"/>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C149" s="16"/>
-    </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C150" s="16"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="94.6640625" bestFit="1" customWidth="1"/>
@@ -7490,7 +4023,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B11" s="9">
         <v>13.952</v>
@@ -7509,7 +4042,7 @@
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -7537,7 +4070,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B13" s="13">
         <v>3.4820000000000001E-4</v>
@@ -7561,7 +4094,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="B14" s="4">
         <v>0.71728999999999998</v>
@@ -7584,7 +4117,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B15" s="15">
         <v>2.9845513851461699E-5</v>
@@ -7603,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -7631,7 +4164,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B17" s="13">
         <v>-1.9897009234307801E-4</v>
@@ -7649,7 +4182,7 @@
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -7666,7 +4199,7 @@
         <v>9</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
@@ -7686,7 +4219,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="G19" t="s">
         <v>31</v>
@@ -7706,7 +4239,7 @@
         <v>9</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
@@ -7727,7 +4260,7 @@
         <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="G21" t="s">
         <v>31</v>
@@ -7748,7 +4281,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="G22" t="s">
         <v>31</v>
@@ -7789,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -7803,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -7906,9 +4439,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B33" s="9">
         <v>1</v>
@@ -7930,7 +4463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -7954,9 +4487,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B35" s="9">
         <v>13.952</v>
@@ -7975,111 +4508,111 @@
         <v>20</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B36" s="9">
-        <f>99.66/100*B21</f>
-        <v>1.4277291599999999</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="17"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="4">
+        <f>0.049232+0.146*B45/0.1*0.9</f>
+        <v>0.23747564000000002</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" t="s">
+        <v>24</v>
+      </c>
       <c r="G36" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="4">
-        <f>0.049232+0.146*B36</f>
-        <v>0.25768045736</v>
+        <v>113</v>
+      </c>
+      <c r="B37" s="13">
+        <v>3.4820000000000001E-4</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F37" s="8"/>
       <c r="G37" t="s">
         <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>128</v>
-      </c>
-      <c r="B38" s="13">
-        <v>3.4820000000000001E-4</v>
+        <v>155</v>
+      </c>
+      <c r="B38" s="4">
+        <v>0.71728999999999998</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="8"/>
       <c r="G38" t="s">
         <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>183</v>
-      </c>
-      <c r="B39" s="4">
-        <v>0.71728999999999998</v>
+        <v>156</v>
+      </c>
+      <c r="B39" s="15">
+        <v>2.9845513851461699E-5</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
+      <c r="F39" s="8"/>
       <c r="G39" t="s">
         <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B40" s="15">
-        <v>2.9845513851461699E-5</v>
+        <v>27</v>
+      </c>
+      <c r="B40" s="13">
+        <v>3.9794018468615601E-10</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
@@ -8088,151 +4621,146 @@
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="8"/>
+        <v>8</v>
+      </c>
       <c r="G40" t="s">
         <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B41" s="13">
-        <v>3.9794018468615601E-10</v>
+        <v>-1.9897009234307801E-4</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
         <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
-        <v>186</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>37</v>
       </c>
       <c r="B42" s="13">
-        <v>-1.9897009234307801E-4</v>
-      </c>
-      <c r="C42" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
+        <v>6.9639532320077196E-4</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="13">
-        <v>6.9639532320077196E-4</v>
+        <v>8.6020242597452001E-2</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>30</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>188</v>
+        <v>21</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="13">
+        <v>1.19382055405847E-4</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="19">
+        <f>0.1*B21</f>
+        <v>0.14326000000000003</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="13">
-        <v>8.6020242597452001E-2</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="B46" s="15">
+        <v>5.4119865117317201E-2</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="13">
-        <v>1.19382055405847E-4</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" s="14"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="22">
-        <f>B21-B36</f>
-        <v>4.8708400000001539E-3</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>188</v>
+      <c r="F46" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="G46" t="s">
         <v>31</v>
       </c>
-      <c r="H46" s="14"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="15">
-        <v>5.4119865117317201E-2</v>
+        <v>32</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0.13927999999999999</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>30</v>
@@ -8241,48 +4769,42 @@
         <v>21</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="G47" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="4">
-        <v>0.13927999999999999</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G48" t="s">
-        <v>31</v>
-      </c>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>119</v>
+      <c r="A50" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -8293,10 +4815,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -8307,10 +4829,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B52" s="8">
+        <v>1</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -8321,10 +4843,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="8">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -8335,10 +4857,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -8348,12 +4870,10 @@
       <c r="H54" s="8"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" t="s">
-        <v>9</v>
-      </c>
+      <c r="A55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -8362,49 +4882,61 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
+      <c r="A56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>12</v>
+      <c r="A57" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" s="9">
+        <v>1</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>14</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="8"/>
       <c r="G57" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>6</v>
+        <v>17</v>
+      </c>
+      <c r="H57" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>119</v>
+      <c r="A58" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="B58" s="9">
-        <v>1</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>16</v>
@@ -8412,23 +4944,23 @@
       <c r="D58" t="s">
         <v>4</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F58" s="8"/>
-      <c r="G58" s="8" t="s">
-        <v>17</v>
+      <c r="G58" t="s">
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="9">
-        <v>0.81499999999999995</v>
+      <c r="A59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="13">
+        <v>5.5099999999999998E-5</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>16</v>
@@ -8436,7 +4968,7 @@
       <c r="D59" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" t="s">
         <v>9</v>
       </c>
       <c r="F59" s="8"/>
@@ -8444,106 +4976,102 @@
         <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="B60" s="13">
-        <v>5.5099999999999998E-5</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>16</v>
+        <v>3.29E-10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
       </c>
       <c r="D60" t="s">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" t="s">
         <v>20</v>
       </c>
       <c r="H60" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="13">
-        <v>3.29E-10</v>
+        <v>32</v>
+      </c>
+      <c r="B61" s="4">
+        <v>0.14899999999999999</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
-      </c>
-      <c r="D61" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
       <c r="G61" t="s">
-        <v>20</v>
-      </c>
-      <c r="H61" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B62" s="4">
-        <v>0.14899999999999999</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>44</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
-      </c>
-      <c r="F62" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="H62" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="4">
-        <v>0.55600000000000005</v>
+        <v>34</v>
+      </c>
+      <c r="B63" s="15">
+        <v>7.67E-4</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="F63" t="s">
+        <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B64" s="15">
-        <v>7.67E-4</v>
+        <v>1.6299999999999999E-3</v>
       </c>
       <c r="C64" t="s">
         <v>30</v>
@@ -8560,10 +5088,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B65" s="15">
-        <v>1.6299999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="C65" t="s">
         <v>30</v>
@@ -8580,16 +5108,17 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B66" s="15">
-        <v>1E-3</v>
+        <f>47.6/1000</f>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="C66" t="s">
         <v>30</v>
       </c>
       <c r="E66" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F66" t="s">
         <v>39</v>
@@ -8603,8 +5132,8 @@
         <v>38</v>
       </c>
       <c r="B67" s="15">
-        <f>47.6/1000</f>
-        <v>4.7600000000000003E-2</v>
+        <f>101/1000</f>
+        <v>0.10100000000000001</v>
       </c>
       <c r="C67" t="s">
         <v>30</v>
@@ -8613,55 +5142,37 @@
         <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G67" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>38</v>
+      <c r="A68" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="B68" s="15">
-        <f>101/1000</f>
-        <v>0.10100000000000001</v>
+        <v>-5.5099999999999998E-5</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="D68" t="s">
+        <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
-      </c>
-      <c r="F68" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B69" s="15">
-        <v>-5.5099999999999998E-5</v>
-      </c>
-      <c r="C69" t="s">
-        <v>18</v>
-      </c>
-      <c r="D69" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G69" t="s">
-        <v>20</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>110</v>
-      </c>
+      <c r="B69" s="15"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B70" s="15"/>
@@ -8673,10 +5184,10 @@
       <c r="B72" s="15"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B73" s="15"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B74" s="4"/>
+      <c r="B74" s="15"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B75" s="15"/>
@@ -8694,16 +5205,13 @@
       <c r="B79" s="15"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B80" s="15"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="8"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="H81" s="8"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="H80" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8711,7 +5219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8729,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -8743,7 +5251,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -8785,7 +5293,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -8848,7 +5356,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B9" s="9">
         <v>1</v>
@@ -8867,7 +5375,7 @@
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -8896,7 +5404,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B11" s="9">
         <v>6.93</v>
@@ -8915,7 +5423,7 @@
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -8943,7 +5451,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B13" s="13">
         <v>3.0000000000000001E-5</v>
@@ -8962,12 +5470,12 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B14" s="13">
         <v>1.0000000000000001E-5</v>
@@ -8986,7 +5494,7 @@
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -9015,7 +5523,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B16" s="13">
         <v>2.0000000000000002E-5</v>
@@ -9063,7 +5571,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B18" s="13">
         <f>0.00020525+0.000034749</f>
@@ -9083,12 +5591,12 @@
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B19" s="13">
         <v>3.7199999999999998E-11</v>
@@ -9106,12 +5614,12 @@
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" s="13">
         <v>9.7999999999999997E-4</v>
@@ -9123,7 +5631,7 @@
         <v>9</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
@@ -9151,7 +5659,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B22" s="13">
         <v>1.9999999999999999E-6</v>
@@ -9183,7 +5691,7 @@
         <v>9</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
@@ -9211,7 +5719,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B25" s="13">
         <v>1.8000000000000001E-4</v>
@@ -9231,7 +5739,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B26" s="15">
         <v>3.0000000000000001E-5</v>
@@ -9251,7 +5759,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B27" s="15">
         <v>2.4000000000000001E-4</v>
@@ -9271,7 +5779,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B28" s="15">
         <v>9.9999999999999995E-7</v>
@@ -9291,7 +5799,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B29" s="15">
         <v>5.2999999999999998E-4</v>
@@ -9303,7 +5811,7 @@
         <v>9</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G29" t="s">
         <v>31</v>
@@ -9331,7 +5839,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B31" s="15">
         <v>2.0000000000000002E-5</v>
@@ -9351,7 +5859,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B32" s="15">
         <v>2.4000000000000001E-4</v>
@@ -9371,7 +5879,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B33" s="15">
         <v>1.38E-5</v>
@@ -9383,7 +5891,7 @@
         <v>9</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G33" t="s">
         <v>31</v>
@@ -9391,7 +5899,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B34" s="15">
         <v>1E-4</v>
@@ -9411,7 +5919,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B35" s="15">
         <v>1.0000000000000001E-5</v>
@@ -9431,7 +5939,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B36" s="15">
         <v>4.8999999999999998E-4</v>
@@ -9452,7 +5960,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B37" s="13">
         <v>1.0000000000000001E-5</v>
@@ -9487,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -9501,7 +6009,7 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -9543,7 +6051,7 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -9606,7 +6114,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B47" s="9">
         <v>1</v>
@@ -9625,7 +6133,7 @@
         <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -9654,9 +6162,9 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B49" s="22">
+        <v>118</v>
+      </c>
+      <c r="B49" s="19">
         <v>6.93</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -9673,7 +6181,7 @@
         <v>20</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -9702,7 +6210,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B51" s="13">
         <v>3.0000000000000001E-5</v>
@@ -9721,12 +6229,12 @@
         <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B52" s="13">
         <v>1.0000000000000001E-5</v>
@@ -9745,7 +6253,7 @@
         <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -9774,7 +6282,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B54" s="13">
         <v>2.0000000000000002E-5</v>
@@ -9822,7 +6330,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B56" s="13">
         <f>0.00020525+0.000034749</f>
@@ -9842,12 +6350,12 @@
         <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B57" s="13">
         <v>3.7199999999999998E-11</v>
@@ -9865,12 +6373,12 @@
         <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B58" s="13">
         <v>9.7999999999999997E-4</v>
@@ -9882,7 +6390,7 @@
         <v>9</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G58" t="s">
         <v>31</v>
@@ -9910,7 +6418,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B60" s="13">
         <v>1.9999999999999999E-6</v>
@@ -9942,7 +6450,7 @@
         <v>9</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G61" t="s">
         <v>31</v>
@@ -9970,7 +6478,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B63" s="13">
         <v>1.8000000000000001E-4</v>
@@ -9990,7 +6498,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B64" s="15">
         <v>3.0000000000000001E-5</v>
@@ -10010,7 +6518,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B65" s="15">
         <v>2.4000000000000001E-4</v>
@@ -10030,7 +6538,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B66" s="15">
         <v>9.9999999999999995E-7</v>
@@ -10050,7 +6558,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B67" s="15">
         <v>5.2999999999999998E-4</v>
@@ -10062,7 +6570,7 @@
         <v>9</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G67" t="s">
         <v>31</v>
@@ -10090,7 +6598,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B69" s="15">
         <v>2.0000000000000002E-5</v>
@@ -10110,7 +6618,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B70" s="15">
         <v>2.4000000000000001E-4</v>
@@ -10130,7 +6638,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B71" s="15">
         <v>1.38E-5</v>
@@ -10142,7 +6650,7 @@
         <v>9</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G71" t="s">
         <v>31</v>
@@ -10150,7 +6658,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B72" s="15">
         <v>1E-4</v>
@@ -10170,7 +6678,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B73" s="15">
         <v>1.0000000000000001E-5</v>
@@ -10190,7 +6698,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B74" s="15">
         <v>4.8999999999999998E-4</v>
@@ -10211,7 +6719,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B75" s="13">
         <v>1.0000000000000001E-5</v>
@@ -10237,7 +6745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10256,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -10264,7 +6772,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -10288,7 +6796,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -10332,7 +6840,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
@@ -10350,12 +6858,12 @@
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B10" s="4">
         <v>2.5190000000000001</v>
@@ -10373,7 +6881,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -10383,7 +6891,7 @@
       <c r="B11" s="4">
         <v>0.14300000000000002</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
@@ -10424,12 +6932,12 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B13" s="4">
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
@@ -10442,7 +6950,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -10452,7 +6960,7 @@
       <c r="B14" s="15">
         <v>2.0789999999999999E-5</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -10510,12 +7018,12 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B17" s="4">
         <v>-1.474E-3</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D17" t="s">
@@ -10528,12 +7036,12 @@
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B18" s="15">
         <v>2.0789999999999999E-5</v>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47F7E86-A444-DC40-83A7-6F3A803B014F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898B220A-02E7-2246-9448-E531F38A62D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -3162,8 +3162,8 @@
         <v>133</v>
       </c>
       <c r="B124" s="9">
-        <f>0.00116842105263158+0.146*B126/0.1*0.9</f>
-        <v>8.9140568526315783E-3</v>
+        <f>0.00116842105263158</f>
+        <v>1.1684210526315801E-3</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898B220A-02E7-2246-9448-E531F38A62D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E08AA7-EC1D-2B40-A01B-E9A75E9F3C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
